--- a/data/excel.xlsx
+++ b/data/excel.xlsx
@@ -1,34 +1,35 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30026"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\abiga\Documents\New project\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3BDA169E-0D56-4749-B47C-5F53A3E34BCC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{14148AB6-FD36-460F-888C-845CCB44B34D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" firstSheet="6" activeTab="8" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="AZUCAR" sheetId="4" r:id="rId1"/>
     <sheet name="GRANOS" sheetId="6" r:id="rId2"/>
-    <sheet name="PLASTICOS" sheetId="9" r:id="rId3"/>
-    <sheet name="MADERA" sheetId="10" r:id="rId4"/>
-    <sheet name="MATERIALES DE CONSTRUCCION" sheetId="7" r:id="rId5"/>
-    <sheet name="PRODUCTOS ELECTRONICOS" sheetId="11" r:id="rId6"/>
-    <sheet name="TELEFONOS CELULARES" sheetId="12" r:id="rId7"/>
-    <sheet name="Hoja1" sheetId="13" r:id="rId8"/>
-    <sheet name="Hoja6" sheetId="8" state="hidden" r:id="rId9"/>
+    <sheet name="Hoja2" sheetId="14" r:id="rId3"/>
+    <sheet name="PLASTICOS" sheetId="9" r:id="rId4"/>
+    <sheet name="MADERA" sheetId="10" r:id="rId5"/>
+    <sheet name="MATERIALES DE CONSTRUCCION" sheetId="7" r:id="rId6"/>
+    <sheet name="PRODUCTOS ELECTRONICOS" sheetId="11" r:id="rId7"/>
+    <sheet name="TELEFONOS CELULARES" sheetId="12" r:id="rId8"/>
+    <sheet name="22415 cod aduanero" sheetId="13" r:id="rId9"/>
+    <sheet name="Hoja6" sheetId="8" state="hidden" r:id="rId10"/>
   </sheets>
   <calcPr calcId="0"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1743" uniqueCount="432">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1752" uniqueCount="437">
   <si>
     <t>Bolsa ingenio</t>
   </si>
@@ -1324,6 +1325,21 @@
   </si>
   <si>
     <t>nueces</t>
+  </si>
+  <si>
+    <t>PRODUCTO</t>
+  </si>
+  <si>
+    <t>HOJA DE COCA</t>
+  </si>
+  <si>
+    <t>KG</t>
+  </si>
+  <si>
+    <t xml:space="preserve">GRAMO </t>
+  </si>
+  <si>
+    <t>CLORHIDRATO DE COCAINA</t>
   </si>
 </sst>
 </file>
@@ -1427,7 +1443,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="19">
+  <cellXfs count="18">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -1464,7 +1480,6 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="3" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
@@ -2047,6 +2062,1580 @@
 </worksheet>
 </file>
 
+<file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1B40AC6E-5AA6-4139-9D9D-0C1E963453B3}">
+  <dimension ref="A1:E103"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetData>
+    <row r="1" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A1" t="s">
+        <v>70</v>
+      </c>
+      <c r="B1" t="s">
+        <v>71</v>
+      </c>
+      <c r="C1" t="s">
+        <v>72</v>
+      </c>
+      <c r="D1" t="s">
+        <v>73</v>
+      </c>
+      <c r="E1" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="2" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A2" t="s">
+        <v>74</v>
+      </c>
+      <c r="B2" t="s">
+        <v>75</v>
+      </c>
+      <c r="C2" t="s">
+        <v>76</v>
+      </c>
+      <c r="D2">
+        <v>12000</v>
+      </c>
+      <c r="E2" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="3" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A3" t="s">
+        <v>74</v>
+      </c>
+      <c r="B3" t="s">
+        <v>78</v>
+      </c>
+      <c r="C3" t="s">
+        <v>79</v>
+      </c>
+      <c r="D3">
+        <v>22000</v>
+      </c>
+      <c r="E3" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="4" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A4" t="s">
+        <v>74</v>
+      </c>
+      <c r="B4" t="s">
+        <v>80</v>
+      </c>
+      <c r="C4" t="s">
+        <v>81</v>
+      </c>
+      <c r="D4">
+        <v>7300</v>
+      </c>
+      <c r="E4" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="5" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A5" t="s">
+        <v>74</v>
+      </c>
+      <c r="B5" t="s">
+        <v>82</v>
+      </c>
+      <c r="C5" t="s">
+        <v>79</v>
+      </c>
+      <c r="D5">
+        <v>9000</v>
+      </c>
+      <c r="E5" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="6" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A6" t="s">
+        <v>74</v>
+      </c>
+      <c r="B6" t="s">
+        <v>83</v>
+      </c>
+      <c r="C6" t="s">
+        <v>79</v>
+      </c>
+      <c r="D6">
+        <v>14000</v>
+      </c>
+      <c r="E6" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="7" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A7" t="s">
+        <v>74</v>
+      </c>
+      <c r="B7" t="s">
+        <v>84</v>
+      </c>
+      <c r="C7" t="s">
+        <v>79</v>
+      </c>
+      <c r="D7">
+        <v>18000</v>
+      </c>
+      <c r="E7" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="8" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A8" t="s">
+        <v>74</v>
+      </c>
+      <c r="B8" t="s">
+        <v>85</v>
+      </c>
+      <c r="C8" t="s">
+        <v>81</v>
+      </c>
+      <c r="D8">
+        <v>15000</v>
+      </c>
+      <c r="E8" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="9" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A9" t="s">
+        <v>74</v>
+      </c>
+      <c r="B9" t="s">
+        <v>86</v>
+      </c>
+      <c r="C9" t="s">
+        <v>81</v>
+      </c>
+      <c r="D9">
+        <v>14000</v>
+      </c>
+      <c r="E9" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="10" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A10" t="s">
+        <v>74</v>
+      </c>
+      <c r="B10" t="s">
+        <v>87</v>
+      </c>
+      <c r="C10" t="s">
+        <v>79</v>
+      </c>
+      <c r="D10">
+        <v>20000</v>
+      </c>
+      <c r="E10" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="11" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A11" t="s">
+        <v>74</v>
+      </c>
+      <c r="B11" t="s">
+        <v>88</v>
+      </c>
+      <c r="C11" t="s">
+        <v>79</v>
+      </c>
+      <c r="D11">
+        <v>16000</v>
+      </c>
+      <c r="E11" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="13" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A13" t="s">
+        <v>89</v>
+      </c>
+      <c r="B13" t="s">
+        <v>90</v>
+      </c>
+      <c r="C13" t="s">
+        <v>91</v>
+      </c>
+      <c r="D13">
+        <v>40000</v>
+      </c>
+      <c r="E13" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="14" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A14" t="s">
+        <v>89</v>
+      </c>
+      <c r="B14" t="s">
+        <v>92</v>
+      </c>
+      <c r="C14" t="s">
+        <v>91</v>
+      </c>
+      <c r="D14">
+        <v>42000</v>
+      </c>
+      <c r="E14" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="15" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A15" t="s">
+        <v>89</v>
+      </c>
+      <c r="B15" t="s">
+        <v>93</v>
+      </c>
+      <c r="C15" t="s">
+        <v>91</v>
+      </c>
+      <c r="D15">
+        <v>45000</v>
+      </c>
+      <c r="E15" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="16" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A16" t="s">
+        <v>89</v>
+      </c>
+      <c r="B16" t="s">
+        <v>94</v>
+      </c>
+      <c r="C16" t="s">
+        <v>91</v>
+      </c>
+      <c r="D16">
+        <v>135000</v>
+      </c>
+      <c r="E16" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="17" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A17" t="s">
+        <v>89</v>
+      </c>
+      <c r="B17" t="s">
+        <v>95</v>
+      </c>
+      <c r="C17" t="s">
+        <v>91</v>
+      </c>
+      <c r="D17">
+        <v>120000</v>
+      </c>
+      <c r="E17" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="18" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A18" t="s">
+        <v>89</v>
+      </c>
+      <c r="B18" t="s">
+        <v>96</v>
+      </c>
+      <c r="C18" t="s">
+        <v>91</v>
+      </c>
+      <c r="D18">
+        <v>105000</v>
+      </c>
+      <c r="E18" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="19" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A19" t="s">
+        <v>89</v>
+      </c>
+      <c r="B19" t="s">
+        <v>97</v>
+      </c>
+      <c r="C19" t="s">
+        <v>91</v>
+      </c>
+      <c r="D19">
+        <v>110000</v>
+      </c>
+      <c r="E19" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="20" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A20" t="s">
+        <v>89</v>
+      </c>
+      <c r="B20" t="s">
+        <v>98</v>
+      </c>
+      <c r="C20" t="s">
+        <v>91</v>
+      </c>
+      <c r="D20">
+        <v>85000</v>
+      </c>
+      <c r="E20" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="21" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A21" t="s">
+        <v>89</v>
+      </c>
+      <c r="B21" t="s">
+        <v>99</v>
+      </c>
+      <c r="C21" t="s">
+        <v>91</v>
+      </c>
+      <c r="D21">
+        <v>65000</v>
+      </c>
+      <c r="E21" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="22" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A22" t="s">
+        <v>89</v>
+      </c>
+      <c r="B22" t="s">
+        <v>100</v>
+      </c>
+      <c r="C22" t="s">
+        <v>91</v>
+      </c>
+      <c r="D22">
+        <v>70000</v>
+      </c>
+      <c r="E22" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="23" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A23" t="s">
+        <v>89</v>
+      </c>
+      <c r="B23" t="s">
+        <v>101</v>
+      </c>
+      <c r="C23" t="s">
+        <v>91</v>
+      </c>
+      <c r="D23">
+        <v>60000</v>
+      </c>
+      <c r="E23" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="25" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A25" t="s">
+        <v>102</v>
+      </c>
+      <c r="B25" t="s">
+        <v>103</v>
+      </c>
+      <c r="C25" t="s">
+        <v>104</v>
+      </c>
+      <c r="D25">
+        <v>230</v>
+      </c>
+      <c r="E25" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="26" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A26" t="s">
+        <v>102</v>
+      </c>
+      <c r="B26" t="s">
+        <v>105</v>
+      </c>
+      <c r="C26" t="s">
+        <v>104</v>
+      </c>
+      <c r="D26">
+        <v>1200</v>
+      </c>
+      <c r="E26" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="27" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A27" t="s">
+        <v>102</v>
+      </c>
+      <c r="B27" t="s">
+        <v>106</v>
+      </c>
+      <c r="C27" t="s">
+        <v>104</v>
+      </c>
+      <c r="D27">
+        <v>1800</v>
+      </c>
+      <c r="E27" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="28" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A28" t="s">
+        <v>102</v>
+      </c>
+      <c r="B28" t="s">
+        <v>107</v>
+      </c>
+      <c r="C28" t="s">
+        <v>104</v>
+      </c>
+      <c r="D28">
+        <v>2500</v>
+      </c>
+      <c r="E28" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="29" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A29" t="s">
+        <v>102</v>
+      </c>
+      <c r="B29" t="s">
+        <v>108</v>
+      </c>
+      <c r="C29" t="s">
+        <v>104</v>
+      </c>
+      <c r="D29">
+        <v>3000</v>
+      </c>
+      <c r="E29" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="30" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A30" t="s">
+        <v>102</v>
+      </c>
+      <c r="B30" t="s">
+        <v>109</v>
+      </c>
+      <c r="C30" t="s">
+        <v>104</v>
+      </c>
+      <c r="D30">
+        <v>2100</v>
+      </c>
+      <c r="E30" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="31" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A31" t="s">
+        <v>102</v>
+      </c>
+      <c r="B31" t="s">
+        <v>110</v>
+      </c>
+      <c r="C31" t="s">
+        <v>104</v>
+      </c>
+      <c r="D31">
+        <v>2500</v>
+      </c>
+      <c r="E31" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="32" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A32" t="s">
+        <v>102</v>
+      </c>
+      <c r="B32" t="s">
+        <v>111</v>
+      </c>
+      <c r="C32" t="s">
+        <v>104</v>
+      </c>
+      <c r="D32">
+        <v>6500</v>
+      </c>
+      <c r="E32" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="33" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A33" t="s">
+        <v>102</v>
+      </c>
+      <c r="B33" t="s">
+        <v>112</v>
+      </c>
+      <c r="C33" t="s">
+        <v>104</v>
+      </c>
+      <c r="D33">
+        <v>3500</v>
+      </c>
+      <c r="E33" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="34" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A34" t="s">
+        <v>102</v>
+      </c>
+      <c r="B34" t="s">
+        <v>113</v>
+      </c>
+      <c r="C34" t="s">
+        <v>104</v>
+      </c>
+      <c r="D34">
+        <v>3200</v>
+      </c>
+      <c r="E34" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="36" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A36" t="s">
+        <v>114</v>
+      </c>
+      <c r="B36" t="s">
+        <v>115</v>
+      </c>
+      <c r="C36" t="s">
+        <v>91</v>
+      </c>
+      <c r="D36">
+        <v>140000</v>
+      </c>
+      <c r="E36" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="37" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A37" t="s">
+        <v>114</v>
+      </c>
+      <c r="B37" t="s">
+        <v>116</v>
+      </c>
+      <c r="C37" t="s">
+        <v>91</v>
+      </c>
+      <c r="D37">
+        <v>135000</v>
+      </c>
+      <c r="E37" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="38" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A38" t="s">
+        <v>114</v>
+      </c>
+      <c r="B38" t="s">
+        <v>117</v>
+      </c>
+      <c r="C38" t="s">
+        <v>91</v>
+      </c>
+      <c r="D38">
+        <v>145000</v>
+      </c>
+      <c r="E38" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="39" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A39" t="s">
+        <v>114</v>
+      </c>
+      <c r="B39" t="s">
+        <v>118</v>
+      </c>
+      <c r="C39" t="s">
+        <v>119</v>
+      </c>
+      <c r="D39">
+        <v>9000</v>
+      </c>
+      <c r="E39" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="40" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A40" t="s">
+        <v>114</v>
+      </c>
+      <c r="B40" t="s">
+        <v>120</v>
+      </c>
+      <c r="C40" t="s">
+        <v>119</v>
+      </c>
+      <c r="D40">
+        <v>11000</v>
+      </c>
+      <c r="E40" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="41" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A41" t="s">
+        <v>114</v>
+      </c>
+      <c r="B41" t="s">
+        <v>121</v>
+      </c>
+      <c r="C41" t="s">
+        <v>104</v>
+      </c>
+      <c r="D41">
+        <v>4500</v>
+      </c>
+      <c r="E41" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="42" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A42" t="s">
+        <v>114</v>
+      </c>
+      <c r="B42" t="s">
+        <v>122</v>
+      </c>
+      <c r="C42" t="s">
+        <v>104</v>
+      </c>
+      <c r="D42">
+        <v>4200</v>
+      </c>
+      <c r="E42" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="43" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A43" t="s">
+        <v>114</v>
+      </c>
+      <c r="B43" t="s">
+        <v>123</v>
+      </c>
+      <c r="C43" t="s">
+        <v>124</v>
+      </c>
+      <c r="D43">
+        <v>55000</v>
+      </c>
+      <c r="E43" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="45" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A45" t="s">
+        <v>125</v>
+      </c>
+      <c r="B45" t="s">
+        <v>126</v>
+      </c>
+      <c r="C45" t="s">
+        <v>127</v>
+      </c>
+      <c r="D45">
+        <v>8000</v>
+      </c>
+      <c r="E45" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="46" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A46" t="s">
+        <v>125</v>
+      </c>
+      <c r="B46" t="s">
+        <v>128</v>
+      </c>
+      <c r="C46" t="s">
+        <v>127</v>
+      </c>
+      <c r="D46">
+        <v>11000</v>
+      </c>
+      <c r="E46" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="47" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A47" t="s">
+        <v>125</v>
+      </c>
+      <c r="B47" t="s">
+        <v>129</v>
+      </c>
+      <c r="C47" t="s">
+        <v>127</v>
+      </c>
+      <c r="D47">
+        <v>15000</v>
+      </c>
+      <c r="E47" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="48" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A48" t="s">
+        <v>125</v>
+      </c>
+      <c r="B48" t="s">
+        <v>130</v>
+      </c>
+      <c r="C48" t="s">
+        <v>127</v>
+      </c>
+      <c r="D48">
+        <v>19000</v>
+      </c>
+      <c r="E48" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="49" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A49" t="s">
+        <v>125</v>
+      </c>
+      <c r="B49" t="s">
+        <v>131</v>
+      </c>
+      <c r="C49" t="s">
+        <v>127</v>
+      </c>
+      <c r="D49">
+        <v>26000</v>
+      </c>
+      <c r="E49" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="50" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A50" t="s">
+        <v>125</v>
+      </c>
+      <c r="B50" t="s">
+        <v>132</v>
+      </c>
+      <c r="C50" t="s">
+        <v>124</v>
+      </c>
+      <c r="D50">
+        <v>10000</v>
+      </c>
+      <c r="E50" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="51" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A51" t="s">
+        <v>125</v>
+      </c>
+      <c r="B51" t="s">
+        <v>133</v>
+      </c>
+      <c r="C51" t="s">
+        <v>134</v>
+      </c>
+      <c r="D51">
+        <v>1600</v>
+      </c>
+      <c r="E51" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="52" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A52" t="s">
+        <v>125</v>
+      </c>
+      <c r="B52" t="s">
+        <v>135</v>
+      </c>
+      <c r="C52" t="s">
+        <v>134</v>
+      </c>
+      <c r="D52">
+        <v>1400</v>
+      </c>
+      <c r="E52" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="53" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A53" t="s">
+        <v>125</v>
+      </c>
+      <c r="B53" t="s">
+        <v>136</v>
+      </c>
+      <c r="C53" t="s">
+        <v>134</v>
+      </c>
+      <c r="D53">
+        <v>2000</v>
+      </c>
+      <c r="E53" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="54" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A54" t="s">
+        <v>125</v>
+      </c>
+      <c r="B54" t="s">
+        <v>137</v>
+      </c>
+      <c r="C54" t="s">
+        <v>119</v>
+      </c>
+      <c r="D54">
+        <v>8500</v>
+      </c>
+      <c r="E54" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="55" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A55" t="s">
+        <v>125</v>
+      </c>
+      <c r="B55" t="s">
+        <v>138</v>
+      </c>
+      <c r="C55" t="s">
+        <v>119</v>
+      </c>
+      <c r="D55">
+        <v>9000</v>
+      </c>
+      <c r="E55" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="56" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A56" t="s">
+        <v>125</v>
+      </c>
+      <c r="B56" t="s">
+        <v>139</v>
+      </c>
+      <c r="C56" t="s">
+        <v>119</v>
+      </c>
+      <c r="D56">
+        <v>12000</v>
+      </c>
+      <c r="E56" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="58" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A58" t="s">
+        <v>140</v>
+      </c>
+      <c r="B58" t="s">
+        <v>141</v>
+      </c>
+      <c r="C58" t="s">
+        <v>124</v>
+      </c>
+      <c r="D58">
+        <v>32000</v>
+      </c>
+      <c r="E58" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="59" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A59" t="s">
+        <v>140</v>
+      </c>
+      <c r="B59" t="s">
+        <v>142</v>
+      </c>
+      <c r="C59" t="s">
+        <v>124</v>
+      </c>
+      <c r="D59">
+        <v>38000</v>
+      </c>
+      <c r="E59" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="60" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A60" t="s">
+        <v>140</v>
+      </c>
+      <c r="B60" t="s">
+        <v>143</v>
+      </c>
+      <c r="C60" t="s">
+        <v>124</v>
+      </c>
+      <c r="D60">
+        <v>45000</v>
+      </c>
+      <c r="E60" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="61" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A61" t="s">
+        <v>140</v>
+      </c>
+      <c r="B61" t="s">
+        <v>144</v>
+      </c>
+      <c r="C61" t="s">
+        <v>124</v>
+      </c>
+      <c r="D61">
+        <v>30000</v>
+      </c>
+      <c r="E61" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="62" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A62" t="s">
+        <v>140</v>
+      </c>
+      <c r="B62" t="s">
+        <v>145</v>
+      </c>
+      <c r="C62" t="s">
+        <v>124</v>
+      </c>
+      <c r="D62">
+        <v>42000</v>
+      </c>
+      <c r="E62" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="64" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A64" t="s">
+        <v>146</v>
+      </c>
+      <c r="B64" t="s">
+        <v>147</v>
+      </c>
+      <c r="C64" t="s">
+        <v>119</v>
+      </c>
+      <c r="D64">
+        <v>9000</v>
+      </c>
+      <c r="E64" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="65" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A65" t="s">
+        <v>146</v>
+      </c>
+      <c r="B65" t="s">
+        <v>148</v>
+      </c>
+      <c r="C65" t="s">
+        <v>119</v>
+      </c>
+      <c r="D65">
+        <v>8000</v>
+      </c>
+      <c r="E65" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="66" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A66" t="s">
+        <v>146</v>
+      </c>
+      <c r="B66" t="s">
+        <v>149</v>
+      </c>
+      <c r="C66" t="s">
+        <v>119</v>
+      </c>
+      <c r="D66">
+        <v>8500</v>
+      </c>
+      <c r="E66" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="67" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A67" t="s">
+        <v>146</v>
+      </c>
+      <c r="B67" t="s">
+        <v>150</v>
+      </c>
+      <c r="C67" t="s">
+        <v>104</v>
+      </c>
+      <c r="D67">
+        <v>18000</v>
+      </c>
+      <c r="E67" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="68" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A68" t="s">
+        <v>146</v>
+      </c>
+      <c r="B68" t="s">
+        <v>151</v>
+      </c>
+      <c r="C68" t="s">
+        <v>124</v>
+      </c>
+      <c r="D68">
+        <v>15000</v>
+      </c>
+      <c r="E68" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="69" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A69" t="s">
+        <v>146</v>
+      </c>
+      <c r="B69" t="s">
+        <v>152</v>
+      </c>
+      <c r="C69" t="s">
+        <v>124</v>
+      </c>
+      <c r="D69">
+        <v>16000</v>
+      </c>
+      <c r="E69" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="70" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A70" t="s">
+        <v>146</v>
+      </c>
+      <c r="B70" t="s">
+        <v>153</v>
+      </c>
+      <c r="C70" t="s">
+        <v>124</v>
+      </c>
+      <c r="D70">
+        <v>20000</v>
+      </c>
+      <c r="E70" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="71" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A71" t="s">
+        <v>146</v>
+      </c>
+      <c r="B71" t="s">
+        <v>154</v>
+      </c>
+      <c r="C71" t="s">
+        <v>124</v>
+      </c>
+      <c r="D71">
+        <v>22000</v>
+      </c>
+      <c r="E71" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="73" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A73" t="s">
+        <v>155</v>
+      </c>
+      <c r="B73" t="s">
+        <v>156</v>
+      </c>
+      <c r="C73" t="s">
+        <v>124</v>
+      </c>
+      <c r="D73">
+        <v>15000</v>
+      </c>
+      <c r="E73" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="74" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A74" t="s">
+        <v>155</v>
+      </c>
+      <c r="B74" t="s">
+        <v>157</v>
+      </c>
+      <c r="C74" t="s">
+        <v>124</v>
+      </c>
+      <c r="D74">
+        <v>19000</v>
+      </c>
+      <c r="E74" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="75" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A75" t="s">
+        <v>155</v>
+      </c>
+      <c r="B75" t="s">
+        <v>158</v>
+      </c>
+      <c r="C75" t="s">
+        <v>124</v>
+      </c>
+      <c r="D75">
+        <v>12000</v>
+      </c>
+      <c r="E75" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="76" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A76" t="s">
+        <v>155</v>
+      </c>
+      <c r="B76" t="s">
+        <v>159</v>
+      </c>
+      <c r="C76" t="s">
+        <v>124</v>
+      </c>
+      <c r="D76">
+        <v>20000</v>
+      </c>
+      <c r="E76" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="77" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A77" t="s">
+        <v>155</v>
+      </c>
+      <c r="B77" t="s">
+        <v>160</v>
+      </c>
+      <c r="C77" t="s">
+        <v>161</v>
+      </c>
+      <c r="D77">
+        <v>55000</v>
+      </c>
+      <c r="E77" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="79" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A79" t="s">
+        <v>162</v>
+      </c>
+      <c r="B79" t="s">
+        <v>163</v>
+      </c>
+      <c r="C79" t="s">
+        <v>124</v>
+      </c>
+      <c r="D79">
+        <v>22000</v>
+      </c>
+      <c r="E79" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="80" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A80" t="s">
+        <v>162</v>
+      </c>
+      <c r="B80" t="s">
+        <v>164</v>
+      </c>
+      <c r="C80" t="s">
+        <v>124</v>
+      </c>
+      <c r="D80">
+        <v>45000</v>
+      </c>
+      <c r="E80" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="81" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A81" t="s">
+        <v>162</v>
+      </c>
+      <c r="B81" t="s">
+        <v>165</v>
+      </c>
+      <c r="C81" t="s">
+        <v>124</v>
+      </c>
+      <c r="D81">
+        <v>28000</v>
+      </c>
+      <c r="E81" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="82" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A82" t="s">
+        <v>162</v>
+      </c>
+      <c r="B82" t="s">
+        <v>166</v>
+      </c>
+      <c r="C82" t="s">
+        <v>124</v>
+      </c>
+      <c r="D82">
+        <v>60000</v>
+      </c>
+      <c r="E82" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="83" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A83" t="s">
+        <v>162</v>
+      </c>
+      <c r="B83" t="s">
+        <v>167</v>
+      </c>
+      <c r="C83" t="s">
+        <v>124</v>
+      </c>
+      <c r="D83">
+        <v>35000</v>
+      </c>
+      <c r="E83" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="85" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A85" t="s">
+        <v>168</v>
+      </c>
+      <c r="B85" t="s">
+        <v>169</v>
+      </c>
+      <c r="C85" t="s">
+        <v>170</v>
+      </c>
+      <c r="D85">
+        <v>90000</v>
+      </c>
+      <c r="E85" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="86" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A86" t="s">
+        <v>168</v>
+      </c>
+      <c r="B86" t="s">
+        <v>171</v>
+      </c>
+      <c r="C86" t="s">
+        <v>170</v>
+      </c>
+      <c r="D86">
+        <v>110000</v>
+      </c>
+      <c r="E86" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="87" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A87" t="s">
+        <v>168</v>
+      </c>
+      <c r="B87" t="s">
+        <v>172</v>
+      </c>
+      <c r="C87" t="s">
+        <v>173</v>
+      </c>
+      <c r="D87">
+        <v>35000</v>
+      </c>
+      <c r="E87" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="88" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A88" t="s">
+        <v>168</v>
+      </c>
+      <c r="B88" t="s">
+        <v>174</v>
+      </c>
+      <c r="C88" t="s">
+        <v>173</v>
+      </c>
+      <c r="D88">
+        <v>30000</v>
+      </c>
+      <c r="E88" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="89" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A89" t="s">
+        <v>168</v>
+      </c>
+      <c r="B89" t="s">
+        <v>175</v>
+      </c>
+      <c r="C89" t="s">
+        <v>170</v>
+      </c>
+      <c r="D89">
+        <v>120000</v>
+      </c>
+      <c r="E89" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="91" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A91" t="s">
+        <v>176</v>
+      </c>
+      <c r="B91" t="s">
+        <v>177</v>
+      </c>
+      <c r="C91" t="s">
+        <v>119</v>
+      </c>
+      <c r="D91">
+        <v>10000</v>
+      </c>
+      <c r="E91" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="92" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A92" t="s">
+        <v>176</v>
+      </c>
+      <c r="B92" t="s">
+        <v>178</v>
+      </c>
+      <c r="C92" t="s">
+        <v>119</v>
+      </c>
+      <c r="D92">
+        <v>7000</v>
+      </c>
+      <c r="E92" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="93" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A93" t="s">
+        <v>176</v>
+      </c>
+      <c r="B93" t="s">
+        <v>179</v>
+      </c>
+      <c r="C93" t="s">
+        <v>104</v>
+      </c>
+      <c r="D93">
+        <v>2500</v>
+      </c>
+      <c r="E93" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="94" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A94" t="s">
+        <v>176</v>
+      </c>
+      <c r="B94" t="s">
+        <v>180</v>
+      </c>
+      <c r="C94" t="s">
+        <v>104</v>
+      </c>
+      <c r="D94">
+        <v>9000</v>
+      </c>
+      <c r="E94" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="95" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A95" t="s">
+        <v>176</v>
+      </c>
+      <c r="B95" t="s">
+        <v>181</v>
+      </c>
+      <c r="C95" t="s">
+        <v>104</v>
+      </c>
+      <c r="D95">
+        <v>55000</v>
+      </c>
+      <c r="E95" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="97" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A97" t="s">
+        <v>182</v>
+      </c>
+      <c r="B97" t="s">
+        <v>183</v>
+      </c>
+      <c r="C97" t="s">
+        <v>119</v>
+      </c>
+      <c r="D97">
+        <v>1200</v>
+      </c>
+      <c r="E97" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="98" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A98" t="s">
+        <v>182</v>
+      </c>
+      <c r="B98" t="s">
+        <v>184</v>
+      </c>
+      <c r="C98" t="s">
+        <v>119</v>
+      </c>
+      <c r="D98">
+        <v>1700</v>
+      </c>
+      <c r="E98" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="99" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A99" t="s">
+        <v>182</v>
+      </c>
+      <c r="B99" t="s">
+        <v>185</v>
+      </c>
+      <c r="C99" t="s">
+        <v>119</v>
+      </c>
+      <c r="D99">
+        <v>800</v>
+      </c>
+      <c r="E99" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="100" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A100" t="s">
+        <v>182</v>
+      </c>
+      <c r="B100" t="s">
+        <v>186</v>
+      </c>
+      <c r="C100" t="s">
+        <v>104</v>
+      </c>
+      <c r="D100">
+        <v>2000</v>
+      </c>
+      <c r="E100" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="101" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A101" t="s">
+        <v>182</v>
+      </c>
+      <c r="B101" t="s">
+        <v>187</v>
+      </c>
+      <c r="C101" t="s">
+        <v>104</v>
+      </c>
+      <c r="D101">
+        <v>35000</v>
+      </c>
+      <c r="E101" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="102" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A102" t="s">
+        <v>182</v>
+      </c>
+      <c r="B102" t="s">
+        <v>188</v>
+      </c>
+      <c r="C102" t="s">
+        <v>104</v>
+      </c>
+      <c r="D102">
+        <v>3500</v>
+      </c>
+      <c r="E102" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="103" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A103" t="s">
+        <v>182</v>
+      </c>
+      <c r="B103" t="s">
+        <v>189</v>
+      </c>
+      <c r="C103" t="s">
+        <v>104</v>
+      </c>
+      <c r="D103">
+        <v>3200</v>
+      </c>
+      <c r="E103" t="s">
+        <v>77</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0756568B-799C-4417-9FD5-CA21567FA36E}">
   <dimension ref="A1:H22"/>
@@ -2339,7 +3928,7 @@
       <c r="F14" s="9" t="s">
         <v>45</v>
       </c>
-      <c r="H14" s="18"/>
+      <c r="H14" s="17"/>
     </row>
     <row r="15" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A15" s="8" t="s">
@@ -2482,7 +4071,7 @@
       </c>
     </row>
     <row r="22" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A22" s="16" t="s">
+      <c r="A22" s="8" t="s">
         <v>35</v>
       </c>
       <c r="B22" s="4" t="s">
@@ -2497,7 +4086,7 @@
       <c r="E22" s="8" t="s">
         <v>53</v>
       </c>
-      <c r="F22" s="17" t="s">
+      <c r="F22" s="16" t="s">
         <v>45</v>
       </c>
     </row>
@@ -2520,6 +4109,15 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{15575E2F-B7E9-4EB5-A791-7D7E5CF1065C}">
+  <dimension ref="A1"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetData/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{CE5B732E-FF65-48B2-A0B0-FFF7B3B5DD44}">
   <dimension ref="A1:E67"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
@@ -3454,7 +5052,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F4933F15-821D-43F0-B734-73373F78EC52}">
   <dimension ref="A1:E78"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
@@ -4745,7 +6343,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B2ED5D93-0BF9-4D0B-A000-F761D38B7B46}">
   <dimension ref="A1:E92"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
@@ -6333,7 +7931,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E658A0D8-3AAB-48EF-8FBD-2662AC5F929D}">
   <dimension ref="A1:E55"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
@@ -7255,7 +8853,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1D8FF1F2-8F62-4B32-A230-1AEFCB8D93C5}">
   <dimension ref="A1:E36"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.7109375" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
@@ -7884,1582 +9482,55 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{748F122F-7CC3-499F-98B9-01D3B28FD4BC}">
-  <dimension ref="A1"/>
+  <dimension ref="A1:E3"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
-  <sheetData/>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1B40AC6E-5AA6-4139-9D9D-0C1E963453B3}">
-  <dimension ref="A1:E103"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="21.5703125" customWidth="1"/>
+    <col min="2" max="2" width="33.7109375" customWidth="1"/>
+    <col min="3" max="3" width="22.42578125" customWidth="1"/>
+    <col min="4" max="4" width="32.7109375" customWidth="1"/>
+    <col min="5" max="5" width="29.7109375" customWidth="1"/>
+  </cols>
   <sheetData>
-    <row r="1" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A1" t="s">
+    <row r="1" spans="1:5" ht="18.75" x14ac:dyDescent="0.3">
+      <c r="A1" s="10" t="s">
         <v>70</v>
       </c>
-      <c r="B1" t="s">
-        <v>71</v>
-      </c>
-      <c r="C1" t="s">
+      <c r="B1" s="10" t="s">
+        <v>432</v>
+      </c>
+      <c r="C1" s="10" t="s">
         <v>72</v>
       </c>
-      <c r="D1" t="s">
+      <c r="D1" s="10" t="s">
         <v>73</v>
       </c>
-      <c r="E1" t="s">
-        <v>34</v>
+      <c r="E1" s="10" t="s">
+        <v>333</v>
       </c>
     </row>
     <row r="2" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A2" t="s">
-        <v>74</v>
-      </c>
       <c r="B2" t="s">
-        <v>75</v>
+        <v>433</v>
       </c>
       <c r="C2" t="s">
-        <v>76</v>
+        <v>434</v>
       </c>
       <c r="D2">
-        <v>12000</v>
-      </c>
-      <c r="E2" t="s">
-        <v>77</v>
+        <v>40000</v>
       </c>
     </row>
     <row r="3" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A3" t="s">
-        <v>74</v>
-      </c>
       <c r="B3" t="s">
-        <v>78</v>
+        <v>436</v>
       </c>
       <c r="C3" t="s">
-        <v>79</v>
+        <v>435</v>
       </c>
       <c r="D3">
-        <v>22000</v>
-      </c>
-      <c r="E3" t="s">
-        <v>77</v>
-      </c>
-    </row>
-    <row r="4" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A4" t="s">
-        <v>74</v>
-      </c>
-      <c r="B4" t="s">
-        <v>80</v>
-      </c>
-      <c r="C4" t="s">
-        <v>81</v>
-      </c>
-      <c r="D4">
-        <v>7300</v>
-      </c>
-      <c r="E4" t="s">
-        <v>77</v>
-      </c>
-    </row>
-    <row r="5" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A5" t="s">
-        <v>74</v>
-      </c>
-      <c r="B5" t="s">
-        <v>82</v>
-      </c>
-      <c r="C5" t="s">
-        <v>79</v>
-      </c>
-      <c r="D5">
-        <v>9000</v>
-      </c>
-      <c r="E5" t="s">
-        <v>77</v>
-      </c>
-    </row>
-    <row r="6" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A6" t="s">
-        <v>74</v>
-      </c>
-      <c r="B6" t="s">
-        <v>83</v>
-      </c>
-      <c r="C6" t="s">
-        <v>79</v>
-      </c>
-      <c r="D6">
         <v>14000</v>
-      </c>
-      <c r="E6" t="s">
-        <v>77</v>
-      </c>
-    </row>
-    <row r="7" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A7" t="s">
-        <v>74</v>
-      </c>
-      <c r="B7" t="s">
-        <v>84</v>
-      </c>
-      <c r="C7" t="s">
-        <v>79</v>
-      </c>
-      <c r="D7">
-        <v>18000</v>
-      </c>
-      <c r="E7" t="s">
-        <v>77</v>
-      </c>
-    </row>
-    <row r="8" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A8" t="s">
-        <v>74</v>
-      </c>
-      <c r="B8" t="s">
-        <v>85</v>
-      </c>
-      <c r="C8" t="s">
-        <v>81</v>
-      </c>
-      <c r="D8">
-        <v>15000</v>
-      </c>
-      <c r="E8" t="s">
-        <v>77</v>
-      </c>
-    </row>
-    <row r="9" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A9" t="s">
-        <v>74</v>
-      </c>
-      <c r="B9" t="s">
-        <v>86</v>
-      </c>
-      <c r="C9" t="s">
-        <v>81</v>
-      </c>
-      <c r="D9">
-        <v>14000</v>
-      </c>
-      <c r="E9" t="s">
-        <v>77</v>
-      </c>
-    </row>
-    <row r="10" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A10" t="s">
-        <v>74</v>
-      </c>
-      <c r="B10" t="s">
-        <v>87</v>
-      </c>
-      <c r="C10" t="s">
-        <v>79</v>
-      </c>
-      <c r="D10">
-        <v>20000</v>
-      </c>
-      <c r="E10" t="s">
-        <v>77</v>
-      </c>
-    </row>
-    <row r="11" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A11" t="s">
-        <v>74</v>
-      </c>
-      <c r="B11" t="s">
-        <v>88</v>
-      </c>
-      <c r="C11" t="s">
-        <v>79</v>
-      </c>
-      <c r="D11">
-        <v>16000</v>
-      </c>
-      <c r="E11" t="s">
-        <v>77</v>
-      </c>
-    </row>
-    <row r="13" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A13" t="s">
-        <v>89</v>
-      </c>
-      <c r="B13" t="s">
-        <v>90</v>
-      </c>
-      <c r="C13" t="s">
-        <v>91</v>
-      </c>
-      <c r="D13">
-        <v>40000</v>
-      </c>
-      <c r="E13" t="s">
-        <v>77</v>
-      </c>
-    </row>
-    <row r="14" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A14" t="s">
-        <v>89</v>
-      </c>
-      <c r="B14" t="s">
-        <v>92</v>
-      </c>
-      <c r="C14" t="s">
-        <v>91</v>
-      </c>
-      <c r="D14">
-        <v>42000</v>
-      </c>
-      <c r="E14" t="s">
-        <v>77</v>
-      </c>
-    </row>
-    <row r="15" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A15" t="s">
-        <v>89</v>
-      </c>
-      <c r="B15" t="s">
-        <v>93</v>
-      </c>
-      <c r="C15" t="s">
-        <v>91</v>
-      </c>
-      <c r="D15">
-        <v>45000</v>
-      </c>
-      <c r="E15" t="s">
-        <v>77</v>
-      </c>
-    </row>
-    <row r="16" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A16" t="s">
-        <v>89</v>
-      </c>
-      <c r="B16" t="s">
-        <v>94</v>
-      </c>
-      <c r="C16" t="s">
-        <v>91</v>
-      </c>
-      <c r="D16">
-        <v>135000</v>
-      </c>
-      <c r="E16" t="s">
-        <v>77</v>
-      </c>
-    </row>
-    <row r="17" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A17" t="s">
-        <v>89</v>
-      </c>
-      <c r="B17" t="s">
-        <v>95</v>
-      </c>
-      <c r="C17" t="s">
-        <v>91</v>
-      </c>
-      <c r="D17">
-        <v>120000</v>
-      </c>
-      <c r="E17" t="s">
-        <v>77</v>
-      </c>
-    </row>
-    <row r="18" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A18" t="s">
-        <v>89</v>
-      </c>
-      <c r="B18" t="s">
-        <v>96</v>
-      </c>
-      <c r="C18" t="s">
-        <v>91</v>
-      </c>
-      <c r="D18">
-        <v>105000</v>
-      </c>
-      <c r="E18" t="s">
-        <v>77</v>
-      </c>
-    </row>
-    <row r="19" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A19" t="s">
-        <v>89</v>
-      </c>
-      <c r="B19" t="s">
-        <v>97</v>
-      </c>
-      <c r="C19" t="s">
-        <v>91</v>
-      </c>
-      <c r="D19">
-        <v>110000</v>
-      </c>
-      <c r="E19" t="s">
-        <v>77</v>
-      </c>
-    </row>
-    <row r="20" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A20" t="s">
-        <v>89</v>
-      </c>
-      <c r="B20" t="s">
-        <v>98</v>
-      </c>
-      <c r="C20" t="s">
-        <v>91</v>
-      </c>
-      <c r="D20">
-        <v>85000</v>
-      </c>
-      <c r="E20" t="s">
-        <v>77</v>
-      </c>
-    </row>
-    <row r="21" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A21" t="s">
-        <v>89</v>
-      </c>
-      <c r="B21" t="s">
-        <v>99</v>
-      </c>
-      <c r="C21" t="s">
-        <v>91</v>
-      </c>
-      <c r="D21">
-        <v>65000</v>
-      </c>
-      <c r="E21" t="s">
-        <v>77</v>
-      </c>
-    </row>
-    <row r="22" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A22" t="s">
-        <v>89</v>
-      </c>
-      <c r="B22" t="s">
-        <v>100</v>
-      </c>
-      <c r="C22" t="s">
-        <v>91</v>
-      </c>
-      <c r="D22">
-        <v>70000</v>
-      </c>
-      <c r="E22" t="s">
-        <v>77</v>
-      </c>
-    </row>
-    <row r="23" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A23" t="s">
-        <v>89</v>
-      </c>
-      <c r="B23" t="s">
-        <v>101</v>
-      </c>
-      <c r="C23" t="s">
-        <v>91</v>
-      </c>
-      <c r="D23">
-        <v>60000</v>
-      </c>
-      <c r="E23" t="s">
-        <v>77</v>
-      </c>
-    </row>
-    <row r="25" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A25" t="s">
-        <v>102</v>
-      </c>
-      <c r="B25" t="s">
-        <v>103</v>
-      </c>
-      <c r="C25" t="s">
-        <v>104</v>
-      </c>
-      <c r="D25">
-        <v>230</v>
-      </c>
-      <c r="E25" t="s">
-        <v>77</v>
-      </c>
-    </row>
-    <row r="26" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A26" t="s">
-        <v>102</v>
-      </c>
-      <c r="B26" t="s">
-        <v>105</v>
-      </c>
-      <c r="C26" t="s">
-        <v>104</v>
-      </c>
-      <c r="D26">
-        <v>1200</v>
-      </c>
-      <c r="E26" t="s">
-        <v>77</v>
-      </c>
-    </row>
-    <row r="27" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A27" t="s">
-        <v>102</v>
-      </c>
-      <c r="B27" t="s">
-        <v>106</v>
-      </c>
-      <c r="C27" t="s">
-        <v>104</v>
-      </c>
-      <c r="D27">
-        <v>1800</v>
-      </c>
-      <c r="E27" t="s">
-        <v>77</v>
-      </c>
-    </row>
-    <row r="28" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A28" t="s">
-        <v>102</v>
-      </c>
-      <c r="B28" t="s">
-        <v>107</v>
-      </c>
-      <c r="C28" t="s">
-        <v>104</v>
-      </c>
-      <c r="D28">
-        <v>2500</v>
-      </c>
-      <c r="E28" t="s">
-        <v>77</v>
-      </c>
-    </row>
-    <row r="29" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A29" t="s">
-        <v>102</v>
-      </c>
-      <c r="B29" t="s">
-        <v>108</v>
-      </c>
-      <c r="C29" t="s">
-        <v>104</v>
-      </c>
-      <c r="D29">
-        <v>3000</v>
-      </c>
-      <c r="E29" t="s">
-        <v>77</v>
-      </c>
-    </row>
-    <row r="30" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A30" t="s">
-        <v>102</v>
-      </c>
-      <c r="B30" t="s">
-        <v>109</v>
-      </c>
-      <c r="C30" t="s">
-        <v>104</v>
-      </c>
-      <c r="D30">
-        <v>2100</v>
-      </c>
-      <c r="E30" t="s">
-        <v>77</v>
-      </c>
-    </row>
-    <row r="31" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A31" t="s">
-        <v>102</v>
-      </c>
-      <c r="B31" t="s">
-        <v>110</v>
-      </c>
-      <c r="C31" t="s">
-        <v>104</v>
-      </c>
-      <c r="D31">
-        <v>2500</v>
-      </c>
-      <c r="E31" t="s">
-        <v>77</v>
-      </c>
-    </row>
-    <row r="32" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A32" t="s">
-        <v>102</v>
-      </c>
-      <c r="B32" t="s">
-        <v>111</v>
-      </c>
-      <c r="C32" t="s">
-        <v>104</v>
-      </c>
-      <c r="D32">
-        <v>6500</v>
-      </c>
-      <c r="E32" t="s">
-        <v>77</v>
-      </c>
-    </row>
-    <row r="33" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A33" t="s">
-        <v>102</v>
-      </c>
-      <c r="B33" t="s">
-        <v>112</v>
-      </c>
-      <c r="C33" t="s">
-        <v>104</v>
-      </c>
-      <c r="D33">
-        <v>3500</v>
-      </c>
-      <c r="E33" t="s">
-        <v>77</v>
-      </c>
-    </row>
-    <row r="34" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A34" t="s">
-        <v>102</v>
-      </c>
-      <c r="B34" t="s">
-        <v>113</v>
-      </c>
-      <c r="C34" t="s">
-        <v>104</v>
-      </c>
-      <c r="D34">
-        <v>3200</v>
-      </c>
-      <c r="E34" t="s">
-        <v>77</v>
-      </c>
-    </row>
-    <row r="36" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A36" t="s">
-        <v>114</v>
-      </c>
-      <c r="B36" t="s">
-        <v>115</v>
-      </c>
-      <c r="C36" t="s">
-        <v>91</v>
-      </c>
-      <c r="D36">
-        <v>140000</v>
-      </c>
-      <c r="E36" t="s">
-        <v>77</v>
-      </c>
-    </row>
-    <row r="37" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A37" t="s">
-        <v>114</v>
-      </c>
-      <c r="B37" t="s">
-        <v>116</v>
-      </c>
-      <c r="C37" t="s">
-        <v>91</v>
-      </c>
-      <c r="D37">
-        <v>135000</v>
-      </c>
-      <c r="E37" t="s">
-        <v>77</v>
-      </c>
-    </row>
-    <row r="38" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A38" t="s">
-        <v>114</v>
-      </c>
-      <c r="B38" t="s">
-        <v>117</v>
-      </c>
-      <c r="C38" t="s">
-        <v>91</v>
-      </c>
-      <c r="D38">
-        <v>145000</v>
-      </c>
-      <c r="E38" t="s">
-        <v>77</v>
-      </c>
-    </row>
-    <row r="39" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A39" t="s">
-        <v>114</v>
-      </c>
-      <c r="B39" t="s">
-        <v>118</v>
-      </c>
-      <c r="C39" t="s">
-        <v>119</v>
-      </c>
-      <c r="D39">
-        <v>9000</v>
-      </c>
-      <c r="E39" t="s">
-        <v>77</v>
-      </c>
-    </row>
-    <row r="40" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A40" t="s">
-        <v>114</v>
-      </c>
-      <c r="B40" t="s">
-        <v>120</v>
-      </c>
-      <c r="C40" t="s">
-        <v>119</v>
-      </c>
-      <c r="D40">
-        <v>11000</v>
-      </c>
-      <c r="E40" t="s">
-        <v>77</v>
-      </c>
-    </row>
-    <row r="41" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A41" t="s">
-        <v>114</v>
-      </c>
-      <c r="B41" t="s">
-        <v>121</v>
-      </c>
-      <c r="C41" t="s">
-        <v>104</v>
-      </c>
-      <c r="D41">
-        <v>4500</v>
-      </c>
-      <c r="E41" t="s">
-        <v>77</v>
-      </c>
-    </row>
-    <row r="42" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A42" t="s">
-        <v>114</v>
-      </c>
-      <c r="B42" t="s">
-        <v>122</v>
-      </c>
-      <c r="C42" t="s">
-        <v>104</v>
-      </c>
-      <c r="D42">
-        <v>4200</v>
-      </c>
-      <c r="E42" t="s">
-        <v>77</v>
-      </c>
-    </row>
-    <row r="43" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A43" t="s">
-        <v>114</v>
-      </c>
-      <c r="B43" t="s">
-        <v>123</v>
-      </c>
-      <c r="C43" t="s">
-        <v>124</v>
-      </c>
-      <c r="D43">
-        <v>55000</v>
-      </c>
-      <c r="E43" t="s">
-        <v>77</v>
-      </c>
-    </row>
-    <row r="45" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A45" t="s">
-        <v>125</v>
-      </c>
-      <c r="B45" t="s">
-        <v>126</v>
-      </c>
-      <c r="C45" t="s">
-        <v>127</v>
-      </c>
-      <c r="D45">
-        <v>8000</v>
-      </c>
-      <c r="E45" t="s">
-        <v>77</v>
-      </c>
-    </row>
-    <row r="46" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A46" t="s">
-        <v>125</v>
-      </c>
-      <c r="B46" t="s">
-        <v>128</v>
-      </c>
-      <c r="C46" t="s">
-        <v>127</v>
-      </c>
-      <c r="D46">
-        <v>11000</v>
-      </c>
-      <c r="E46" t="s">
-        <v>77</v>
-      </c>
-    </row>
-    <row r="47" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A47" t="s">
-        <v>125</v>
-      </c>
-      <c r="B47" t="s">
-        <v>129</v>
-      </c>
-      <c r="C47" t="s">
-        <v>127</v>
-      </c>
-      <c r="D47">
-        <v>15000</v>
-      </c>
-      <c r="E47" t="s">
-        <v>77</v>
-      </c>
-    </row>
-    <row r="48" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A48" t="s">
-        <v>125</v>
-      </c>
-      <c r="B48" t="s">
-        <v>130</v>
-      </c>
-      <c r="C48" t="s">
-        <v>127</v>
-      </c>
-      <c r="D48">
-        <v>19000</v>
-      </c>
-      <c r="E48" t="s">
-        <v>77</v>
-      </c>
-    </row>
-    <row r="49" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A49" t="s">
-        <v>125</v>
-      </c>
-      <c r="B49" t="s">
-        <v>131</v>
-      </c>
-      <c r="C49" t="s">
-        <v>127</v>
-      </c>
-      <c r="D49">
-        <v>26000</v>
-      </c>
-      <c r="E49" t="s">
-        <v>77</v>
-      </c>
-    </row>
-    <row r="50" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A50" t="s">
-        <v>125</v>
-      </c>
-      <c r="B50" t="s">
-        <v>132</v>
-      </c>
-      <c r="C50" t="s">
-        <v>124</v>
-      </c>
-      <c r="D50">
-        <v>10000</v>
-      </c>
-      <c r="E50" t="s">
-        <v>77</v>
-      </c>
-    </row>
-    <row r="51" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A51" t="s">
-        <v>125</v>
-      </c>
-      <c r="B51" t="s">
-        <v>133</v>
-      </c>
-      <c r="C51" t="s">
-        <v>134</v>
-      </c>
-      <c r="D51">
-        <v>1600</v>
-      </c>
-      <c r="E51" t="s">
-        <v>77</v>
-      </c>
-    </row>
-    <row r="52" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A52" t="s">
-        <v>125</v>
-      </c>
-      <c r="B52" t="s">
-        <v>135</v>
-      </c>
-      <c r="C52" t="s">
-        <v>134</v>
-      </c>
-      <c r="D52">
-        <v>1400</v>
-      </c>
-      <c r="E52" t="s">
-        <v>77</v>
-      </c>
-    </row>
-    <row r="53" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A53" t="s">
-        <v>125</v>
-      </c>
-      <c r="B53" t="s">
-        <v>136</v>
-      </c>
-      <c r="C53" t="s">
-        <v>134</v>
-      </c>
-      <c r="D53">
-        <v>2000</v>
-      </c>
-      <c r="E53" t="s">
-        <v>77</v>
-      </c>
-    </row>
-    <row r="54" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A54" t="s">
-        <v>125</v>
-      </c>
-      <c r="B54" t="s">
-        <v>137</v>
-      </c>
-      <c r="C54" t="s">
-        <v>119</v>
-      </c>
-      <c r="D54">
-        <v>8500</v>
-      </c>
-      <c r="E54" t="s">
-        <v>77</v>
-      </c>
-    </row>
-    <row r="55" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A55" t="s">
-        <v>125</v>
-      </c>
-      <c r="B55" t="s">
-        <v>138</v>
-      </c>
-      <c r="C55" t="s">
-        <v>119</v>
-      </c>
-      <c r="D55">
-        <v>9000</v>
-      </c>
-      <c r="E55" t="s">
-        <v>77</v>
-      </c>
-    </row>
-    <row r="56" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A56" t="s">
-        <v>125</v>
-      </c>
-      <c r="B56" t="s">
-        <v>139</v>
-      </c>
-      <c r="C56" t="s">
-        <v>119</v>
-      </c>
-      <c r="D56">
-        <v>12000</v>
-      </c>
-      <c r="E56" t="s">
-        <v>77</v>
-      </c>
-    </row>
-    <row r="58" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A58" t="s">
-        <v>140</v>
-      </c>
-      <c r="B58" t="s">
-        <v>141</v>
-      </c>
-      <c r="C58" t="s">
-        <v>124</v>
-      </c>
-      <c r="D58">
-        <v>32000</v>
-      </c>
-      <c r="E58" t="s">
-        <v>77</v>
-      </c>
-    </row>
-    <row r="59" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A59" t="s">
-        <v>140</v>
-      </c>
-      <c r="B59" t="s">
-        <v>142</v>
-      </c>
-      <c r="C59" t="s">
-        <v>124</v>
-      </c>
-      <c r="D59">
-        <v>38000</v>
-      </c>
-      <c r="E59" t="s">
-        <v>77</v>
-      </c>
-    </row>
-    <row r="60" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A60" t="s">
-        <v>140</v>
-      </c>
-      <c r="B60" t="s">
-        <v>143</v>
-      </c>
-      <c r="C60" t="s">
-        <v>124</v>
-      </c>
-      <c r="D60">
-        <v>45000</v>
-      </c>
-      <c r="E60" t="s">
-        <v>77</v>
-      </c>
-    </row>
-    <row r="61" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A61" t="s">
-        <v>140</v>
-      </c>
-      <c r="B61" t="s">
-        <v>144</v>
-      </c>
-      <c r="C61" t="s">
-        <v>124</v>
-      </c>
-      <c r="D61">
-        <v>30000</v>
-      </c>
-      <c r="E61" t="s">
-        <v>77</v>
-      </c>
-    </row>
-    <row r="62" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A62" t="s">
-        <v>140</v>
-      </c>
-      <c r="B62" t="s">
-        <v>145</v>
-      </c>
-      <c r="C62" t="s">
-        <v>124</v>
-      </c>
-      <c r="D62">
-        <v>42000</v>
-      </c>
-      <c r="E62" t="s">
-        <v>77</v>
-      </c>
-    </row>
-    <row r="64" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A64" t="s">
-        <v>146</v>
-      </c>
-      <c r="B64" t="s">
-        <v>147</v>
-      </c>
-      <c r="C64" t="s">
-        <v>119</v>
-      </c>
-      <c r="D64">
-        <v>9000</v>
-      </c>
-      <c r="E64" t="s">
-        <v>77</v>
-      </c>
-    </row>
-    <row r="65" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A65" t="s">
-        <v>146</v>
-      </c>
-      <c r="B65" t="s">
-        <v>148</v>
-      </c>
-      <c r="C65" t="s">
-        <v>119</v>
-      </c>
-      <c r="D65">
-        <v>8000</v>
-      </c>
-      <c r="E65" t="s">
-        <v>77</v>
-      </c>
-    </row>
-    <row r="66" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A66" t="s">
-        <v>146</v>
-      </c>
-      <c r="B66" t="s">
-        <v>149</v>
-      </c>
-      <c r="C66" t="s">
-        <v>119</v>
-      </c>
-      <c r="D66">
-        <v>8500</v>
-      </c>
-      <c r="E66" t="s">
-        <v>77</v>
-      </c>
-    </row>
-    <row r="67" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A67" t="s">
-        <v>146</v>
-      </c>
-      <c r="B67" t="s">
-        <v>150</v>
-      </c>
-      <c r="C67" t="s">
-        <v>104</v>
-      </c>
-      <c r="D67">
-        <v>18000</v>
-      </c>
-      <c r="E67" t="s">
-        <v>77</v>
-      </c>
-    </row>
-    <row r="68" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A68" t="s">
-        <v>146</v>
-      </c>
-      <c r="B68" t="s">
-        <v>151</v>
-      </c>
-      <c r="C68" t="s">
-        <v>124</v>
-      </c>
-      <c r="D68">
-        <v>15000</v>
-      </c>
-      <c r="E68" t="s">
-        <v>77</v>
-      </c>
-    </row>
-    <row r="69" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A69" t="s">
-        <v>146</v>
-      </c>
-      <c r="B69" t="s">
-        <v>152</v>
-      </c>
-      <c r="C69" t="s">
-        <v>124</v>
-      </c>
-      <c r="D69">
-        <v>16000</v>
-      </c>
-      <c r="E69" t="s">
-        <v>77</v>
-      </c>
-    </row>
-    <row r="70" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A70" t="s">
-        <v>146</v>
-      </c>
-      <c r="B70" t="s">
-        <v>153</v>
-      </c>
-      <c r="C70" t="s">
-        <v>124</v>
-      </c>
-      <c r="D70">
-        <v>20000</v>
-      </c>
-      <c r="E70" t="s">
-        <v>77</v>
-      </c>
-    </row>
-    <row r="71" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A71" t="s">
-        <v>146</v>
-      </c>
-      <c r="B71" t="s">
-        <v>154</v>
-      </c>
-      <c r="C71" t="s">
-        <v>124</v>
-      </c>
-      <c r="D71">
-        <v>22000</v>
-      </c>
-      <c r="E71" t="s">
-        <v>77</v>
-      </c>
-    </row>
-    <row r="73" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A73" t="s">
-        <v>155</v>
-      </c>
-      <c r="B73" t="s">
-        <v>156</v>
-      </c>
-      <c r="C73" t="s">
-        <v>124</v>
-      </c>
-      <c r="D73">
-        <v>15000</v>
-      </c>
-      <c r="E73" t="s">
-        <v>77</v>
-      </c>
-    </row>
-    <row r="74" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A74" t="s">
-        <v>155</v>
-      </c>
-      <c r="B74" t="s">
-        <v>157</v>
-      </c>
-      <c r="C74" t="s">
-        <v>124</v>
-      </c>
-      <c r="D74">
-        <v>19000</v>
-      </c>
-      <c r="E74" t="s">
-        <v>77</v>
-      </c>
-    </row>
-    <row r="75" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A75" t="s">
-        <v>155</v>
-      </c>
-      <c r="B75" t="s">
-        <v>158</v>
-      </c>
-      <c r="C75" t="s">
-        <v>124</v>
-      </c>
-      <c r="D75">
-        <v>12000</v>
-      </c>
-      <c r="E75" t="s">
-        <v>77</v>
-      </c>
-    </row>
-    <row r="76" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A76" t="s">
-        <v>155</v>
-      </c>
-      <c r="B76" t="s">
-        <v>159</v>
-      </c>
-      <c r="C76" t="s">
-        <v>124</v>
-      </c>
-      <c r="D76">
-        <v>20000</v>
-      </c>
-      <c r="E76" t="s">
-        <v>77</v>
-      </c>
-    </row>
-    <row r="77" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A77" t="s">
-        <v>155</v>
-      </c>
-      <c r="B77" t="s">
-        <v>160</v>
-      </c>
-      <c r="C77" t="s">
-        <v>161</v>
-      </c>
-      <c r="D77">
-        <v>55000</v>
-      </c>
-      <c r="E77" t="s">
-        <v>77</v>
-      </c>
-    </row>
-    <row r="79" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A79" t="s">
-        <v>162</v>
-      </c>
-      <c r="B79" t="s">
-        <v>163</v>
-      </c>
-      <c r="C79" t="s">
-        <v>124</v>
-      </c>
-      <c r="D79">
-        <v>22000</v>
-      </c>
-      <c r="E79" t="s">
-        <v>77</v>
-      </c>
-    </row>
-    <row r="80" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A80" t="s">
-        <v>162</v>
-      </c>
-      <c r="B80" t="s">
-        <v>164</v>
-      </c>
-      <c r="C80" t="s">
-        <v>124</v>
-      </c>
-      <c r="D80">
-        <v>45000</v>
-      </c>
-      <c r="E80" t="s">
-        <v>77</v>
-      </c>
-    </row>
-    <row r="81" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A81" t="s">
-        <v>162</v>
-      </c>
-      <c r="B81" t="s">
-        <v>165</v>
-      </c>
-      <c r="C81" t="s">
-        <v>124</v>
-      </c>
-      <c r="D81">
-        <v>28000</v>
-      </c>
-      <c r="E81" t="s">
-        <v>77</v>
-      </c>
-    </row>
-    <row r="82" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A82" t="s">
-        <v>162</v>
-      </c>
-      <c r="B82" t="s">
-        <v>166</v>
-      </c>
-      <c r="C82" t="s">
-        <v>124</v>
-      </c>
-      <c r="D82">
-        <v>60000</v>
-      </c>
-      <c r="E82" t="s">
-        <v>77</v>
-      </c>
-    </row>
-    <row r="83" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A83" t="s">
-        <v>162</v>
-      </c>
-      <c r="B83" t="s">
-        <v>167</v>
-      </c>
-      <c r="C83" t="s">
-        <v>124</v>
-      </c>
-      <c r="D83">
-        <v>35000</v>
-      </c>
-      <c r="E83" t="s">
-        <v>77</v>
-      </c>
-    </row>
-    <row r="85" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A85" t="s">
-        <v>168</v>
-      </c>
-      <c r="B85" t="s">
-        <v>169</v>
-      </c>
-      <c r="C85" t="s">
-        <v>170</v>
-      </c>
-      <c r="D85">
-        <v>90000</v>
-      </c>
-      <c r="E85" t="s">
-        <v>77</v>
-      </c>
-    </row>
-    <row r="86" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A86" t="s">
-        <v>168</v>
-      </c>
-      <c r="B86" t="s">
-        <v>171</v>
-      </c>
-      <c r="C86" t="s">
-        <v>170</v>
-      </c>
-      <c r="D86">
-        <v>110000</v>
-      </c>
-      <c r="E86" t="s">
-        <v>77</v>
-      </c>
-    </row>
-    <row r="87" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A87" t="s">
-        <v>168</v>
-      </c>
-      <c r="B87" t="s">
-        <v>172</v>
-      </c>
-      <c r="C87" t="s">
-        <v>173</v>
-      </c>
-      <c r="D87">
-        <v>35000</v>
-      </c>
-      <c r="E87" t="s">
-        <v>77</v>
-      </c>
-    </row>
-    <row r="88" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A88" t="s">
-        <v>168</v>
-      </c>
-      <c r="B88" t="s">
-        <v>174</v>
-      </c>
-      <c r="C88" t="s">
-        <v>173</v>
-      </c>
-      <c r="D88">
-        <v>30000</v>
-      </c>
-      <c r="E88" t="s">
-        <v>77</v>
-      </c>
-    </row>
-    <row r="89" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A89" t="s">
-        <v>168</v>
-      </c>
-      <c r="B89" t="s">
-        <v>175</v>
-      </c>
-      <c r="C89" t="s">
-        <v>170</v>
-      </c>
-      <c r="D89">
-        <v>120000</v>
-      </c>
-      <c r="E89" t="s">
-        <v>77</v>
-      </c>
-    </row>
-    <row r="91" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A91" t="s">
-        <v>176</v>
-      </c>
-      <c r="B91" t="s">
-        <v>177</v>
-      </c>
-      <c r="C91" t="s">
-        <v>119</v>
-      </c>
-      <c r="D91">
-        <v>10000</v>
-      </c>
-      <c r="E91" t="s">
-        <v>77</v>
-      </c>
-    </row>
-    <row r="92" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A92" t="s">
-        <v>176</v>
-      </c>
-      <c r="B92" t="s">
-        <v>178</v>
-      </c>
-      <c r="C92" t="s">
-        <v>119</v>
-      </c>
-      <c r="D92">
-        <v>7000</v>
-      </c>
-      <c r="E92" t="s">
-        <v>77</v>
-      </c>
-    </row>
-    <row r="93" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A93" t="s">
-        <v>176</v>
-      </c>
-      <c r="B93" t="s">
-        <v>179</v>
-      </c>
-      <c r="C93" t="s">
-        <v>104</v>
-      </c>
-      <c r="D93">
-        <v>2500</v>
-      </c>
-      <c r="E93" t="s">
-        <v>77</v>
-      </c>
-    </row>
-    <row r="94" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A94" t="s">
-        <v>176</v>
-      </c>
-      <c r="B94" t="s">
-        <v>180</v>
-      </c>
-      <c r="C94" t="s">
-        <v>104</v>
-      </c>
-      <c r="D94">
-        <v>9000</v>
-      </c>
-      <c r="E94" t="s">
-        <v>77</v>
-      </c>
-    </row>
-    <row r="95" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A95" t="s">
-        <v>176</v>
-      </c>
-      <c r="B95" t="s">
-        <v>181</v>
-      </c>
-      <c r="C95" t="s">
-        <v>104</v>
-      </c>
-      <c r="D95">
-        <v>55000</v>
-      </c>
-      <c r="E95" t="s">
-        <v>77</v>
-      </c>
-    </row>
-    <row r="97" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A97" t="s">
-        <v>182</v>
-      </c>
-      <c r="B97" t="s">
-        <v>183</v>
-      </c>
-      <c r="C97" t="s">
-        <v>119</v>
-      </c>
-      <c r="D97">
-        <v>1200</v>
-      </c>
-      <c r="E97" t="s">
-        <v>77</v>
-      </c>
-    </row>
-    <row r="98" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A98" t="s">
-        <v>182</v>
-      </c>
-      <c r="B98" t="s">
-        <v>184</v>
-      </c>
-      <c r="C98" t="s">
-        <v>119</v>
-      </c>
-      <c r="D98">
-        <v>1700</v>
-      </c>
-      <c r="E98" t="s">
-        <v>77</v>
-      </c>
-    </row>
-    <row r="99" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A99" t="s">
-        <v>182</v>
-      </c>
-      <c r="B99" t="s">
-        <v>185</v>
-      </c>
-      <c r="C99" t="s">
-        <v>119</v>
-      </c>
-      <c r="D99">
-        <v>800</v>
-      </c>
-      <c r="E99" t="s">
-        <v>77</v>
-      </c>
-    </row>
-    <row r="100" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A100" t="s">
-        <v>182</v>
-      </c>
-      <c r="B100" t="s">
-        <v>186</v>
-      </c>
-      <c r="C100" t="s">
-        <v>104</v>
-      </c>
-      <c r="D100">
-        <v>2000</v>
-      </c>
-      <c r="E100" t="s">
-        <v>77</v>
-      </c>
-    </row>
-    <row r="101" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A101" t="s">
-        <v>182</v>
-      </c>
-      <c r="B101" t="s">
-        <v>187</v>
-      </c>
-      <c r="C101" t="s">
-        <v>104</v>
-      </c>
-      <c r="D101">
-        <v>35000</v>
-      </c>
-      <c r="E101" t="s">
-        <v>77</v>
-      </c>
-    </row>
-    <row r="102" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A102" t="s">
-        <v>182</v>
-      </c>
-      <c r="B102" t="s">
-        <v>188</v>
-      </c>
-      <c r="C102" t="s">
-        <v>104</v>
-      </c>
-      <c r="D102">
-        <v>3500</v>
-      </c>
-      <c r="E102" t="s">
-        <v>77</v>
-      </c>
-    </row>
-    <row r="103" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A103" t="s">
-        <v>182</v>
-      </c>
-      <c r="B103" t="s">
-        <v>189</v>
-      </c>
-      <c r="C103" t="s">
-        <v>104</v>
-      </c>
-      <c r="D103">
-        <v>3200</v>
-      </c>
-      <c r="E103" t="s">
-        <v>77</v>
       </c>
     </row>
   </sheetData>

--- a/data/excel.xlsx
+++ b/data/excel.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\abiga\Documents\New project\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{14148AB6-FD36-460F-888C-845CCB44B34D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{83B04751-224A-48D2-BFE7-BBE420DAE3B1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" firstSheet="6" activeTab="8" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" firstSheet="1" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="AZUCAR" sheetId="4" r:id="rId1"/>
@@ -29,7 +29,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1752" uniqueCount="437">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1763" uniqueCount="439">
   <si>
     <t>Bolsa ingenio</t>
   </si>
@@ -1340,6 +1340,12 @@
   </si>
   <si>
     <t>CLORHIDRATO DE COCAINA</t>
+  </si>
+  <si>
+    <t>estupefaciente</t>
+  </si>
+  <si>
+    <t>planta </t>
   </si>
 </sst>
 </file>
@@ -1350,7 +1356,7 @@
     <numFmt numFmtId="6" formatCode="&quot;$&quot;\ #,##0;[Red]\-&quot;$&quot;\ #,##0"/>
     <numFmt numFmtId="8" formatCode="&quot;$&quot;\ #,##0.00;[Red]\-&quot;$&quot;\ #,##0.00"/>
   </numFmts>
-  <fonts count="5" x14ac:knownFonts="1">
+  <fonts count="6" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -1386,6 +1392,11 @@
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="12"/>
+      <name val="Arial"/>
+      <family val="2"/>
     </font>
   </fonts>
   <fills count="3">
@@ -1443,7 +1454,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="18">
+  <cellXfs count="20">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -1484,6 +1495,8 @@
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Hipervínculo" xfId="1" builtinId="8"/>
@@ -4110,10 +4123,65 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{15575E2F-B7E9-4EB5-A791-7D7E5CF1065C}">
-  <dimension ref="A1"/>
+  <dimension ref="A1:E6"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
-  <sheetData/>
+  <cols>
+    <col min="1" max="1" width="17.7109375" customWidth="1"/>
+    <col min="2" max="2" width="32.7109375" customWidth="1"/>
+    <col min="5" max="5" width="23.7109375" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:5" ht="18.75" x14ac:dyDescent="0.3">
+      <c r="A1" s="7" t="s">
+        <v>49</v>
+      </c>
+      <c r="B1" s="10" t="s">
+        <v>50</v>
+      </c>
+      <c r="C1" s="10" t="s">
+        <v>51</v>
+      </c>
+      <c r="D1" s="10" t="s">
+        <v>52</v>
+      </c>
+      <c r="E1" s="10" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="2" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A2" s="18" t="s">
+        <v>438</v>
+      </c>
+      <c r="B2" t="s">
+        <v>433</v>
+      </c>
+      <c r="C2" t="s">
+        <v>434</v>
+      </c>
+      <c r="D2">
+        <v>40000</v>
+      </c>
+    </row>
+    <row r="3" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A3" t="s">
+        <v>437</v>
+      </c>
+      <c r="B3" t="s">
+        <v>436</v>
+      </c>
+      <c r="C3" t="s">
+        <v>435</v>
+      </c>
+      <c r="D3">
+        <v>14000</v>
+      </c>
+    </row>
+    <row r="6" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="B6" s="19"/>
+    </row>
+  </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" horizontalDpi="360" verticalDpi="360" r:id="rId1"/>
 </worksheet>
 </file>
 

--- a/data/excel.xlsx
+++ b/data/excel.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\abiga\Documents\New project\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{83B04751-224A-48D2-BFE7-BBE420DAE3B1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{22B8FEE6-582F-4717-8221-B66C94B19A99}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" firstSheet="1" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="AZUCAR" sheetId="4" r:id="rId1"/>
@@ -29,7 +29,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1763" uniqueCount="439">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1771" uniqueCount="443">
   <si>
     <t>Bolsa ingenio</t>
   </si>
@@ -1346,6 +1346,18 @@
   </si>
   <si>
     <t>planta </t>
+  </si>
+  <si>
+    <t>https://informatesalta.com.ar/sociedad/la-hoja-de-coca-subio-un-30--y-se-consigue-el-kilo-de-la-hojeada-hasta--45-000_a6a15916a03d1047930dc412f</t>
+  </si>
+  <si>
+    <t>https://ccadicciones.es/cuanto-se-paga-en-cada-pais-por-un-gramo-de-cocaina/</t>
+  </si>
+  <si>
+    <t>PLANTA</t>
+  </si>
+  <si>
+    <t>SUSTANCIA</t>
   </si>
 </sst>
 </file>
@@ -1454,7 +1466,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="20">
+  <cellXfs count="21">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -1497,6 +1509,7 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Hipervínculo" xfId="1" builtinId="8"/>
@@ -5122,7 +5135,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F4933F15-821D-43F0-B734-73373F78EC52}">
-  <dimension ref="A1:E78"/>
+  <dimension ref="A1:E74"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="25.140625" customWidth="1"/>
@@ -5286,24 +5299,34 @@
       </c>
     </row>
     <row r="10" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A10" s="8"/>
-      <c r="B10" s="8"/>
-      <c r="C10" s="4"/>
-      <c r="D10" s="4"/>
-      <c r="E10" s="8"/>
+      <c r="A10" s="8" t="s">
+        <v>266</v>
+      </c>
+      <c r="B10" s="8" t="s">
+        <v>267</v>
+      </c>
+      <c r="C10" s="4" t="s">
+        <v>91</v>
+      </c>
+      <c r="D10">
+        <v>1300000</v>
+      </c>
+      <c r="E10" s="9" t="s">
+        <v>77</v>
+      </c>
     </row>
     <row r="11" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A11" s="8" t="s">
         <v>266</v>
       </c>
       <c r="B11" s="8" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="C11" s="4" t="s">
         <v>91</v>
       </c>
       <c r="D11">
-        <v>1300000</v>
+        <v>950000</v>
       </c>
       <c r="E11" s="9" t="s">
         <v>77</v>
@@ -5314,13 +5337,13 @@
         <v>266</v>
       </c>
       <c r="B12" s="8" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="C12" s="4" t="s">
         <v>91</v>
       </c>
       <c r="D12">
-        <v>950000</v>
+        <v>900000</v>
       </c>
       <c r="E12" s="9" t="s">
         <v>77</v>
@@ -5331,13 +5354,13 @@
         <v>266</v>
       </c>
       <c r="B13" s="8" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="C13" s="4" t="s">
         <v>91</v>
       </c>
       <c r="D13">
-        <v>900000</v>
+        <v>820000</v>
       </c>
       <c r="E13" s="9" t="s">
         <v>77</v>
@@ -5348,13 +5371,13 @@
         <v>266</v>
       </c>
       <c r="B14" s="8" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="C14" s="4" t="s">
         <v>91</v>
       </c>
       <c r="D14">
-        <v>820000</v>
+        <v>700000</v>
       </c>
       <c r="E14" s="9" t="s">
         <v>77</v>
@@ -5365,13 +5388,13 @@
         <v>266</v>
       </c>
       <c r="B15" s="8" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="C15" s="4" t="s">
         <v>91</v>
       </c>
       <c r="D15">
-        <v>700000</v>
+        <v>750000</v>
       </c>
       <c r="E15" s="9" t="s">
         <v>77</v>
@@ -5382,13 +5405,13 @@
         <v>266</v>
       </c>
       <c r="B16" s="8" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="C16" s="4" t="s">
         <v>91</v>
       </c>
       <c r="D16">
-        <v>750000</v>
+        <v>680000</v>
       </c>
       <c r="E16" s="9" t="s">
         <v>77</v>
@@ -5399,13 +5422,13 @@
         <v>266</v>
       </c>
       <c r="B17" s="8" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="C17" s="4" t="s">
         <v>91</v>
       </c>
       <c r="D17">
-        <v>680000</v>
+        <v>1600000</v>
       </c>
       <c r="E17" s="9" t="s">
         <v>77</v>
@@ -5416,13 +5439,13 @@
         <v>266</v>
       </c>
       <c r="B18" s="8" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="C18" s="4" t="s">
         <v>91</v>
       </c>
       <c r="D18">
-        <v>1600000</v>
+        <v>1000000</v>
       </c>
       <c r="E18" s="9" t="s">
         <v>77</v>
@@ -5433,13 +5456,13 @@
         <v>266</v>
       </c>
       <c r="B19" s="8" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="C19" s="4" t="s">
         <v>91</v>
       </c>
       <c r="D19">
-        <v>1000000</v>
+        <v>900000</v>
       </c>
       <c r="E19" s="9" t="s">
         <v>77</v>
@@ -5450,13 +5473,13 @@
         <v>266</v>
       </c>
       <c r="B20" s="8" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="C20" s="4" t="s">
         <v>91</v>
       </c>
       <c r="D20">
-        <v>900000</v>
+        <v>680000</v>
       </c>
       <c r="E20" s="9" t="s">
         <v>77</v>
@@ -5467,13 +5490,13 @@
         <v>266</v>
       </c>
       <c r="B21" s="8" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="C21" s="4" t="s">
         <v>91</v>
       </c>
       <c r="D21">
-        <v>680000</v>
+        <v>650000</v>
       </c>
       <c r="E21" s="9" t="s">
         <v>77</v>
@@ -5484,13 +5507,13 @@
         <v>266</v>
       </c>
       <c r="B22" s="8" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="C22" s="4" t="s">
         <v>91</v>
       </c>
       <c r="D22">
-        <v>650000</v>
+        <v>780000</v>
       </c>
       <c r="E22" s="9" t="s">
         <v>77</v>
@@ -5501,54 +5524,54 @@
         <v>266</v>
       </c>
       <c r="B23" s="8" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="C23" s="4" t="s">
         <v>91</v>
       </c>
       <c r="D23">
-        <v>780000</v>
+        <v>850000</v>
       </c>
       <c r="E23" s="9" t="s">
         <v>77</v>
       </c>
     </row>
     <row r="24" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A24" s="8" t="s">
-        <v>266</v>
-      </c>
-      <c r="B24" s="8" t="s">
-        <v>280</v>
-      </c>
-      <c r="C24" s="4" t="s">
-        <v>91</v>
-      </c>
-      <c r="D24">
-        <v>850000</v>
-      </c>
-      <c r="E24" s="9" t="s">
-        <v>77</v>
-      </c>
+      <c r="A24" s="8"/>
+      <c r="B24" s="8"/>
+      <c r="C24" s="4"/>
+      <c r="D24" s="4"/>
+      <c r="E24" s="8"/>
     </row>
     <row r="25" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A25" s="8"/>
-      <c r="B25" s="8"/>
-      <c r="C25" s="4"/>
-      <c r="D25" s="4"/>
-      <c r="E25" s="8"/>
+      <c r="A25" s="8" t="s">
+        <v>281</v>
+      </c>
+      <c r="B25" s="8" t="s">
+        <v>282</v>
+      </c>
+      <c r="C25" s="4" t="s">
+        <v>119</v>
+      </c>
+      <c r="D25">
+        <v>20000</v>
+      </c>
+      <c r="E25" s="9" t="s">
+        <v>77</v>
+      </c>
     </row>
     <row r="26" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A26" s="8" t="s">
         <v>281</v>
       </c>
       <c r="B26" s="8" t="s">
-        <v>282</v>
+        <v>149</v>
       </c>
       <c r="C26" s="4" t="s">
         <v>119</v>
       </c>
       <c r="D26">
-        <v>20000</v>
+        <v>9500</v>
       </c>
       <c r="E26" s="9" t="s">
         <v>77</v>
@@ -5559,13 +5582,13 @@
         <v>281</v>
       </c>
       <c r="B27" s="8" t="s">
-        <v>149</v>
+        <v>283</v>
       </c>
       <c r="C27" s="4" t="s">
         <v>119</v>
       </c>
       <c r="D27">
-        <v>9500</v>
+        <v>5000</v>
       </c>
       <c r="E27" s="9" t="s">
         <v>77</v>
@@ -5576,13 +5599,13 @@
         <v>281</v>
       </c>
       <c r="B28" s="8" t="s">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="C28" s="4" t="s">
-        <v>119</v>
+        <v>104</v>
       </c>
       <c r="D28">
-        <v>5000</v>
+        <v>28000</v>
       </c>
       <c r="E28" s="9" t="s">
         <v>77</v>
@@ -5593,13 +5616,13 @@
         <v>281</v>
       </c>
       <c r="B29" s="8" t="s">
-        <v>284</v>
+        <v>150</v>
       </c>
       <c r="C29" s="4" t="s">
         <v>104</v>
       </c>
       <c r="D29">
-        <v>28000</v>
+        <v>22000</v>
       </c>
       <c r="E29" s="9" t="s">
         <v>77</v>
@@ -5610,13 +5633,13 @@
         <v>281</v>
       </c>
       <c r="B30" s="8" t="s">
-        <v>150</v>
+        <v>285</v>
       </c>
       <c r="C30" s="4" t="s">
         <v>104</v>
       </c>
       <c r="D30">
-        <v>22000</v>
+        <v>17000</v>
       </c>
       <c r="E30" s="9" t="s">
         <v>77</v>
@@ -5627,13 +5650,13 @@
         <v>281</v>
       </c>
       <c r="B31" s="8" t="s">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="C31" s="4" t="s">
-        <v>104</v>
+        <v>119</v>
       </c>
       <c r="D31">
-        <v>17000</v>
+        <v>27000</v>
       </c>
       <c r="E31" s="9" t="s">
         <v>77</v>
@@ -5641,40 +5664,50 @@
     </row>
     <row r="32" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A32" s="8" t="s">
-        <v>281</v>
+        <v>287</v>
       </c>
       <c r="B32" s="8" t="s">
-        <v>286</v>
+        <v>153</v>
       </c>
       <c r="C32" s="4" t="s">
-        <v>119</v>
+        <v>124</v>
       </c>
       <c r="D32">
-        <v>27000</v>
+        <v>22000</v>
       </c>
       <c r="E32" s="9" t="s">
         <v>77</v>
       </c>
     </row>
     <row r="33" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A33" s="8"/>
-      <c r="B33" s="8"/>
-      <c r="C33" s="4"/>
-      <c r="D33" s="4"/>
-      <c r="E33" s="8"/>
+      <c r="A33" s="8" t="s">
+        <v>287</v>
+      </c>
+      <c r="B33" s="8" t="s">
+        <v>288</v>
+      </c>
+      <c r="C33" s="4" t="s">
+        <v>124</v>
+      </c>
+      <c r="D33" s="15">
+        <v>24000</v>
+      </c>
+      <c r="E33" s="9" t="s">
+        <v>77</v>
+      </c>
     </row>
     <row r="34" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A34" s="8" t="s">
         <v>287</v>
       </c>
       <c r="B34" s="8" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="C34" s="4" t="s">
         <v>124</v>
       </c>
       <c r="D34">
-        <v>22000</v>
+        <v>18000</v>
       </c>
       <c r="E34" s="9" t="s">
         <v>77</v>
@@ -5685,13 +5718,13 @@
         <v>287</v>
       </c>
       <c r="B35" s="8" t="s">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="C35" s="4" t="s">
         <v>124</v>
       </c>
-      <c r="D35" s="15">
-        <v>24000</v>
+      <c r="D35">
+        <v>20000</v>
       </c>
       <c r="E35" s="9" t="s">
         <v>77</v>
@@ -5702,13 +5735,13 @@
         <v>287</v>
       </c>
       <c r="B36" s="8" t="s">
-        <v>152</v>
+        <v>290</v>
       </c>
       <c r="C36" s="4" t="s">
         <v>124</v>
       </c>
       <c r="D36">
-        <v>18000</v>
+        <v>23000</v>
       </c>
       <c r="E36" s="9" t="s">
         <v>77</v>
@@ -5719,13 +5752,13 @@
         <v>287</v>
       </c>
       <c r="B37" s="8" t="s">
-        <v>289</v>
+        <v>291</v>
       </c>
       <c r="C37" s="4" t="s">
         <v>124</v>
       </c>
       <c r="D37">
-        <v>20000</v>
+        <v>30000</v>
       </c>
       <c r="E37" s="9" t="s">
         <v>77</v>
@@ -5736,13 +5769,13 @@
         <v>287</v>
       </c>
       <c r="B38" s="8" t="s">
-        <v>290</v>
+        <v>292</v>
       </c>
       <c r="C38" s="4" t="s">
         <v>124</v>
       </c>
       <c r="D38">
-        <v>23000</v>
+        <v>28000</v>
       </c>
       <c r="E38" s="9" t="s">
         <v>77</v>
@@ -5753,13 +5786,13 @@
         <v>287</v>
       </c>
       <c r="B39" s="8" t="s">
-        <v>291</v>
+        <v>293</v>
       </c>
       <c r="C39" s="4" t="s">
         <v>124</v>
       </c>
       <c r="D39">
-        <v>30000</v>
+        <v>27000</v>
       </c>
       <c r="E39" s="9" t="s">
         <v>77</v>
@@ -5770,13 +5803,13 @@
         <v>287</v>
       </c>
       <c r="B40" s="8" t="s">
-        <v>292</v>
+        <v>294</v>
       </c>
       <c r="C40" s="4" t="s">
         <v>124</v>
       </c>
       <c r="D40">
-        <v>28000</v>
+        <v>26000</v>
       </c>
       <c r="E40" s="9" t="s">
         <v>77</v>
@@ -5787,13 +5820,13 @@
         <v>287</v>
       </c>
       <c r="B41" s="8" t="s">
-        <v>293</v>
+        <v>295</v>
       </c>
       <c r="C41" s="4" t="s">
         <v>124</v>
       </c>
       <c r="D41">
-        <v>27000</v>
+        <v>32000</v>
       </c>
       <c r="E41" s="9" t="s">
         <v>77</v>
@@ -5801,16 +5834,16 @@
     </row>
     <row r="42" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A42" s="8" t="s">
-        <v>287</v>
+        <v>296</v>
       </c>
       <c r="B42" s="8" t="s">
-        <v>294</v>
+        <v>297</v>
       </c>
       <c r="C42" s="4" t="s">
         <v>124</v>
       </c>
-      <c r="D42">
-        <v>26000</v>
+      <c r="D42" s="4">
+        <v>17000</v>
       </c>
       <c r="E42" s="9" t="s">
         <v>77</v>
@@ -5818,40 +5851,50 @@
     </row>
     <row r="43" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A43" s="8" t="s">
-        <v>287</v>
+        <v>296</v>
       </c>
       <c r="B43" s="8" t="s">
-        <v>295</v>
+        <v>298</v>
       </c>
       <c r="C43" s="4" t="s">
         <v>124</v>
       </c>
-      <c r="D43">
-        <v>32000</v>
+      <c r="D43" s="4">
+        <v>48000</v>
       </c>
       <c r="E43" s="9" t="s">
         <v>77</v>
       </c>
     </row>
     <row r="44" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A44" s="8"/>
-      <c r="B44" s="8"/>
-      <c r="C44" s="4"/>
-      <c r="D44" s="4"/>
-      <c r="E44" s="8"/>
+      <c r="A44" s="8" t="s">
+        <v>296</v>
+      </c>
+      <c r="B44" s="8" t="s">
+        <v>299</v>
+      </c>
+      <c r="C44" s="4" t="s">
+        <v>124</v>
+      </c>
+      <c r="D44" s="4">
+        <v>34000</v>
+      </c>
+      <c r="E44" s="9" t="s">
+        <v>77</v>
+      </c>
     </row>
     <row r="45" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A45" s="8" t="s">
         <v>296</v>
       </c>
       <c r="B45" s="8" t="s">
-        <v>297</v>
+        <v>300</v>
       </c>
       <c r="C45" s="4" t="s">
         <v>124</v>
       </c>
       <c r="D45" s="4">
-        <v>17000</v>
+        <v>51000</v>
       </c>
       <c r="E45" s="9" t="s">
         <v>77</v>
@@ -5862,13 +5905,13 @@
         <v>296</v>
       </c>
       <c r="B46" s="8" t="s">
-        <v>298</v>
+        <v>301</v>
       </c>
       <c r="C46" s="4" t="s">
-        <v>124</v>
+        <v>91</v>
       </c>
       <c r="D46" s="4">
-        <v>48000</v>
+        <v>460000</v>
       </c>
       <c r="E46" s="9" t="s">
         <v>77</v>
@@ -5879,13 +5922,13 @@
         <v>296</v>
       </c>
       <c r="B47" s="8" t="s">
-        <v>299</v>
+        <v>302</v>
       </c>
       <c r="C47" s="4" t="s">
-        <v>124</v>
+        <v>91</v>
       </c>
       <c r="D47" s="4">
-        <v>34000</v>
+        <v>450000</v>
       </c>
       <c r="E47" s="9" t="s">
         <v>77</v>
@@ -5896,13 +5939,13 @@
         <v>296</v>
       </c>
       <c r="B48" s="8" t="s">
-        <v>300</v>
+        <v>303</v>
       </c>
       <c r="C48" s="4" t="s">
-        <v>124</v>
+        <v>119</v>
       </c>
       <c r="D48" s="4">
-        <v>51000</v>
+        <v>10000</v>
       </c>
       <c r="E48" s="9" t="s">
         <v>77</v>
@@ -5913,13 +5956,13 @@
         <v>296</v>
       </c>
       <c r="B49" s="8" t="s">
-        <v>301</v>
+        <v>304</v>
       </c>
       <c r="C49" s="4" t="s">
         <v>91</v>
       </c>
       <c r="D49" s="4">
-        <v>460000</v>
+        <v>510000</v>
       </c>
       <c r="E49" s="9" t="s">
         <v>77</v>
@@ -5927,16 +5970,16 @@
     </row>
     <row r="50" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A50" s="8" t="s">
-        <v>296</v>
+        <v>305</v>
       </c>
       <c r="B50" s="8" t="s">
-        <v>302</v>
+        <v>306</v>
       </c>
       <c r="C50" s="4" t="s">
-        <v>91</v>
+        <v>104</v>
       </c>
       <c r="D50" s="4">
-        <v>450000</v>
+        <v>140000</v>
       </c>
       <c r="E50" s="9" t="s">
         <v>77</v>
@@ -5944,16 +5987,16 @@
     </row>
     <row r="51" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A51" s="8" t="s">
-        <v>296</v>
+        <v>305</v>
       </c>
       <c r="B51" s="8" t="s">
-        <v>303</v>
+        <v>307</v>
       </c>
       <c r="C51" s="4" t="s">
-        <v>119</v>
+        <v>104</v>
       </c>
       <c r="D51" s="4">
-        <v>10000</v>
+        <v>95000</v>
       </c>
       <c r="E51" s="9" t="s">
         <v>77</v>
@@ -5961,40 +6004,50 @@
     </row>
     <row r="52" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A52" s="8" t="s">
-        <v>296</v>
+        <v>305</v>
       </c>
       <c r="B52" s="8" t="s">
-        <v>304</v>
+        <v>308</v>
       </c>
       <c r="C52" s="4" t="s">
-        <v>91</v>
+        <v>104</v>
       </c>
       <c r="D52" s="4">
-        <v>510000</v>
+        <v>40000</v>
       </c>
       <c r="E52" s="9" t="s">
         <v>77</v>
       </c>
     </row>
     <row r="53" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A53" s="8"/>
-      <c r="B53" s="8"/>
-      <c r="C53" s="4"/>
-      <c r="D53" s="4"/>
-      <c r="E53" s="8"/>
+      <c r="A53" s="8" t="s">
+        <v>305</v>
+      </c>
+      <c r="B53" s="8" t="s">
+        <v>309</v>
+      </c>
+      <c r="C53" s="4" t="s">
+        <v>119</v>
+      </c>
+      <c r="D53" s="4">
+        <v>5000</v>
+      </c>
+      <c r="E53" s="9" t="s">
+        <v>77</v>
+      </c>
     </row>
     <row r="54" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A54" s="8" t="s">
         <v>305</v>
       </c>
       <c r="B54" s="8" t="s">
-        <v>306</v>
+        <v>310</v>
       </c>
       <c r="C54" s="4" t="s">
-        <v>104</v>
+        <v>119</v>
       </c>
       <c r="D54" s="4">
-        <v>140000</v>
+        <v>5000</v>
       </c>
       <c r="E54" s="9" t="s">
         <v>77</v>
@@ -6005,13 +6058,13 @@
         <v>305</v>
       </c>
       <c r="B55" s="8" t="s">
-        <v>307</v>
+        <v>311</v>
       </c>
       <c r="C55" s="4" t="s">
         <v>104</v>
       </c>
       <c r="D55" s="4">
-        <v>95000</v>
+        <v>22000</v>
       </c>
       <c r="E55" s="9" t="s">
         <v>77</v>
@@ -6022,13 +6075,13 @@
         <v>305</v>
       </c>
       <c r="B56" s="8" t="s">
-        <v>308</v>
+        <v>312</v>
       </c>
       <c r="C56" s="4" t="s">
-        <v>104</v>
+        <v>119</v>
       </c>
       <c r="D56" s="4">
-        <v>40000</v>
+        <v>22000</v>
       </c>
       <c r="E56" s="9" t="s">
         <v>77</v>
@@ -6039,13 +6092,13 @@
         <v>305</v>
       </c>
       <c r="B57" s="8" t="s">
-        <v>309</v>
+        <v>313</v>
       </c>
       <c r="C57" s="4" t="s">
-        <v>119</v>
+        <v>124</v>
       </c>
       <c r="D57" s="4">
-        <v>5000</v>
+        <v>55000</v>
       </c>
       <c r="E57" s="9" t="s">
         <v>77</v>
@@ -6056,13 +6109,13 @@
         <v>305</v>
       </c>
       <c r="B58" s="8" t="s">
-        <v>310</v>
+        <v>314</v>
       </c>
       <c r="C58" s="4" t="s">
-        <v>119</v>
+        <v>104</v>
       </c>
       <c r="D58" s="4">
-        <v>5000</v>
+        <v>180000</v>
       </c>
       <c r="E58" s="9" t="s">
         <v>77</v>
@@ -6070,16 +6123,16 @@
     </row>
     <row r="59" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A59" s="8" t="s">
-        <v>305</v>
+        <v>315</v>
       </c>
       <c r="B59" s="8" t="s">
-        <v>311</v>
+        <v>316</v>
       </c>
       <c r="C59" s="4" t="s">
-        <v>104</v>
+        <v>134</v>
       </c>
       <c r="D59" s="4">
-        <v>22000</v>
+        <v>450</v>
       </c>
       <c r="E59" s="9" t="s">
         <v>77</v>
@@ -6087,16 +6140,16 @@
     </row>
     <row r="60" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A60" s="8" t="s">
-        <v>305</v>
+        <v>315</v>
       </c>
       <c r="B60" s="8" t="s">
-        <v>312</v>
+        <v>317</v>
       </c>
       <c r="C60" s="4" t="s">
-        <v>119</v>
+        <v>134</v>
       </c>
       <c r="D60" s="4">
-        <v>22000</v>
+        <v>150</v>
       </c>
       <c r="E60" s="9" t="s">
         <v>77</v>
@@ -6104,16 +6157,16 @@
     </row>
     <row r="61" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A61" s="8" t="s">
-        <v>305</v>
+        <v>315</v>
       </c>
       <c r="B61" s="8" t="s">
-        <v>313</v>
+        <v>318</v>
       </c>
       <c r="C61" s="4" t="s">
-        <v>124</v>
+        <v>134</v>
       </c>
       <c r="D61" s="4">
-        <v>55000</v>
+        <v>250</v>
       </c>
       <c r="E61" s="9" t="s">
         <v>77</v>
@@ -6121,40 +6174,50 @@
     </row>
     <row r="62" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A62" s="8" t="s">
-        <v>305</v>
+        <v>315</v>
       </c>
       <c r="B62" s="8" t="s">
-        <v>314</v>
+        <v>319</v>
       </c>
       <c r="C62" s="4" t="s">
-        <v>104</v>
+        <v>134</v>
       </c>
       <c r="D62" s="4">
-        <v>180000</v>
+        <v>1200</v>
       </c>
       <c r="E62" s="9" t="s">
         <v>77</v>
       </c>
     </row>
     <row r="63" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A63" s="8"/>
-      <c r="B63" s="8"/>
-      <c r="C63" s="4"/>
-      <c r="D63" s="4"/>
-      <c r="E63" s="8"/>
+      <c r="A63" s="8" t="s">
+        <v>315</v>
+      </c>
+      <c r="B63" s="8" t="s">
+        <v>320</v>
+      </c>
+      <c r="C63" s="4" t="s">
+        <v>134</v>
+      </c>
+      <c r="D63" s="4">
+        <v>350</v>
+      </c>
+      <c r="E63" s="9" t="s">
+        <v>77</v>
+      </c>
     </row>
     <row r="64" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A64" s="8" t="s">
         <v>315</v>
       </c>
       <c r="B64" s="8" t="s">
-        <v>316</v>
+        <v>321</v>
       </c>
       <c r="C64" s="4" t="s">
         <v>134</v>
       </c>
       <c r="D64" s="4">
-        <v>450</v>
+        <v>300</v>
       </c>
       <c r="E64" s="9" t="s">
         <v>77</v>
@@ -6165,13 +6228,13 @@
         <v>315</v>
       </c>
       <c r="B65" s="8" t="s">
-        <v>317</v>
+        <v>322</v>
       </c>
       <c r="C65" s="4" t="s">
         <v>134</v>
       </c>
       <c r="D65" s="4">
-        <v>150</v>
+        <v>500</v>
       </c>
       <c r="E65" s="9" t="s">
         <v>77</v>
@@ -6179,16 +6242,16 @@
     </row>
     <row r="66" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A66" s="8" t="s">
-        <v>315</v>
+        <v>323</v>
       </c>
       <c r="B66" s="8" t="s">
-        <v>318</v>
+        <v>324</v>
       </c>
       <c r="C66" s="4" t="s">
         <v>134</v>
       </c>
       <c r="D66" s="4">
-        <v>250</v>
+        <v>1300</v>
       </c>
       <c r="E66" s="9" t="s">
         <v>77</v>
@@ -6196,16 +6259,16 @@
     </row>
     <row r="67" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A67" s="8" t="s">
-        <v>315</v>
+        <v>323</v>
       </c>
       <c r="B67" s="8" t="s">
-        <v>319</v>
+        <v>325</v>
       </c>
       <c r="C67" s="4" t="s">
         <v>134</v>
       </c>
       <c r="D67" s="4">
-        <v>1200</v>
+        <v>1000</v>
       </c>
       <c r="E67" s="9" t="s">
         <v>77</v>
@@ -6213,16 +6276,16 @@
     </row>
     <row r="68" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A68" s="8" t="s">
-        <v>315</v>
+        <v>323</v>
       </c>
       <c r="B68" s="8" t="s">
-        <v>320</v>
+        <v>326</v>
       </c>
       <c r="C68" s="4" t="s">
         <v>134</v>
       </c>
       <c r="D68" s="4">
-        <v>350</v>
+        <v>1000</v>
       </c>
       <c r="E68" s="9" t="s">
         <v>77</v>
@@ -6230,16 +6293,16 @@
     </row>
     <row r="69" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A69" s="8" t="s">
-        <v>315</v>
+        <v>323</v>
       </c>
       <c r="B69" s="8" t="s">
-        <v>321</v>
+        <v>327</v>
       </c>
       <c r="C69" s="4" t="s">
         <v>134</v>
       </c>
       <c r="D69" s="4">
-        <v>300</v>
+        <v>700</v>
       </c>
       <c r="E69" s="9" t="s">
         <v>77</v>
@@ -6247,165 +6310,107 @@
     </row>
     <row r="70" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A70" s="8" t="s">
-        <v>315</v>
+        <v>323</v>
       </c>
       <c r="B70" s="8" t="s">
-        <v>322</v>
+        <v>328</v>
       </c>
       <c r="C70" s="4" t="s">
         <v>134</v>
       </c>
       <c r="D70" s="4">
-        <v>500</v>
+        <v>950</v>
       </c>
       <c r="E70" s="9" t="s">
         <v>77</v>
       </c>
     </row>
     <row r="71" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A71" s="8"/>
-      <c r="B71" s="8"/>
-      <c r="C71" s="4"/>
-      <c r="D71" s="4"/>
-      <c r="E71" s="8"/>
+      <c r="A71" s="8" t="s">
+        <v>323</v>
+      </c>
+      <c r="B71" s="8" t="s">
+        <v>329</v>
+      </c>
+      <c r="C71" s="4" t="s">
+        <v>134</v>
+      </c>
+      <c r="D71" s="4">
+        <v>1000</v>
+      </c>
+      <c r="E71" s="9" t="s">
+        <v>77</v>
+      </c>
     </row>
     <row r="72" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A72" s="8" t="s">
         <v>323</v>
       </c>
       <c r="B72" s="8" t="s">
-        <v>324</v>
+        <v>330</v>
       </c>
       <c r="C72" s="4" t="s">
         <v>134</v>
       </c>
       <c r="D72" s="4">
-        <v>1300</v>
+        <v>1200</v>
       </c>
       <c r="E72" s="9" t="s">
         <v>77</v>
       </c>
     </row>
-    <row r="73" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A73" s="8" t="s">
-        <v>323</v>
+    <row r="73" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A73" s="20" t="s">
+        <v>441</v>
       </c>
       <c r="B73" s="8" t="s">
-        <v>325</v>
-      </c>
-      <c r="C73" s="4" t="s">
-        <v>134</v>
-      </c>
-      <c r="D73" s="4">
-        <v>1000</v>
-      </c>
-      <c r="E73" s="9" t="s">
-        <v>77</v>
+        <v>433</v>
+      </c>
+      <c r="C73" s="8" t="s">
+        <v>434</v>
+      </c>
+      <c r="D73" s="8">
+        <v>40000</v>
+      </c>
+      <c r="E73" s="8" t="s">
+        <v>439</v>
       </c>
     </row>
     <row r="74" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A74" s="8" t="s">
-        <v>323</v>
+        <v>442</v>
       </c>
       <c r="B74" s="8" t="s">
-        <v>326</v>
-      </c>
-      <c r="C74" s="4" t="s">
-        <v>134</v>
-      </c>
-      <c r="D74" s="4">
-        <v>1000</v>
-      </c>
-      <c r="E74" s="9" t="s">
-        <v>77</v>
-      </c>
-    </row>
-    <row r="75" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A75" s="8" t="s">
-        <v>323</v>
-      </c>
-      <c r="B75" s="8" t="s">
-        <v>327</v>
-      </c>
-      <c r="C75" s="4" t="s">
-        <v>134</v>
-      </c>
-      <c r="D75" s="4">
-        <v>700</v>
-      </c>
-      <c r="E75" s="9" t="s">
-        <v>77</v>
-      </c>
-    </row>
-    <row r="76" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A76" s="8" t="s">
-        <v>323</v>
-      </c>
-      <c r="B76" s="8" t="s">
-        <v>328</v>
-      </c>
-      <c r="C76" s="4" t="s">
-        <v>134</v>
-      </c>
-      <c r="D76" s="4">
-        <v>950</v>
-      </c>
-      <c r="E76" s="9" t="s">
-        <v>77</v>
-      </c>
-    </row>
-    <row r="77" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A77" s="8" t="s">
-        <v>323</v>
-      </c>
-      <c r="B77" s="8" t="s">
-        <v>329</v>
-      </c>
-      <c r="C77" s="4" t="s">
-        <v>134</v>
-      </c>
-      <c r="D77" s="4">
-        <v>1000</v>
-      </c>
-      <c r="E77" s="9" t="s">
-        <v>77</v>
-      </c>
-    </row>
-    <row r="78" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A78" s="8" t="s">
-        <v>323</v>
-      </c>
-      <c r="B78" s="8" t="s">
-        <v>330</v>
-      </c>
-      <c r="C78" s="4" t="s">
-        <v>134</v>
-      </c>
-      <c r="D78" s="4">
-        <v>1200</v>
-      </c>
-      <c r="E78" s="9" t="s">
-        <v>77</v>
+        <v>436</v>
+      </c>
+      <c r="C74" s="8" t="s">
+        <v>435</v>
+      </c>
+      <c r="D74" s="8">
+        <v>14000</v>
+      </c>
+      <c r="E74" t="s">
+        <v>440</v>
       </c>
     </row>
   </sheetData>
   <hyperlinks>
     <hyperlink ref="E2" r:id="rId1" xr:uid="{64BB0AA9-1164-47C5-B632-3806012F736E}"/>
     <hyperlink ref="E3:E9" r:id="rId2" display="https://www.indec.gob.ar" xr:uid="{1F70C952-D5A5-47AF-9A4B-CF2093B5E271}"/>
-    <hyperlink ref="E11" r:id="rId3" xr:uid="{4B9E5B17-A56A-422A-B590-67760E263D92}"/>
-    <hyperlink ref="E12:E24" r:id="rId4" display="https://www.indec.gob.ar" xr:uid="{3B42FCC9-8808-4EDE-93A7-F0228BD41018}"/>
-    <hyperlink ref="E26" r:id="rId5" xr:uid="{7362EF37-2A22-4D09-8EC4-151BA22CDD08}"/>
-    <hyperlink ref="E27:E32" r:id="rId6" display="https://www.indec.gob.ar" xr:uid="{181371F1-EAAE-4810-8933-9D89CDD1928B}"/>
-    <hyperlink ref="E34" r:id="rId7" xr:uid="{9297117E-8D72-4F38-9F1C-0AA5B4696F0A}"/>
-    <hyperlink ref="E35:E43" r:id="rId8" display="https://www.indec.gob.ar" xr:uid="{2806D78C-8E30-4025-9799-F7DF1797C643}"/>
-    <hyperlink ref="E45" r:id="rId9" xr:uid="{9F861BF9-FBE3-4D68-BAC0-EAA35FE9FB34}"/>
-    <hyperlink ref="E46:E52" r:id="rId10" display="https://www.indec.gob.ar" xr:uid="{C9E4B419-0DE6-4110-AEFE-A82E1CB79C2F}"/>
-    <hyperlink ref="E54" r:id="rId11" xr:uid="{15FAFF3D-2F48-4076-88AA-BBA4C2B7EC2D}"/>
-    <hyperlink ref="E55:E62" r:id="rId12" display="https://www.indec.gob.ar" xr:uid="{9E9E376A-2A8A-4C3F-B19F-8187BBFF29A6}"/>
-    <hyperlink ref="E64" r:id="rId13" xr:uid="{83A6D2E9-840C-4217-AB1D-DE5830B04CDA}"/>
-    <hyperlink ref="E65:E70" r:id="rId14" display="https://www.indec.gob.ar" xr:uid="{379F007A-C006-46C2-9D3D-C0EC7A5EF762}"/>
-    <hyperlink ref="E72" r:id="rId15" xr:uid="{4F7F4EDC-5326-48FD-A346-11471096DAC6}"/>
-    <hyperlink ref="E73:E78" r:id="rId16" display="https://www.indec.gob.ar" xr:uid="{6B2DAFC2-2A0B-447C-A2C3-C95C48E79112}"/>
+    <hyperlink ref="E10" r:id="rId3" xr:uid="{4B9E5B17-A56A-422A-B590-67760E263D92}"/>
+    <hyperlink ref="E11:E23" r:id="rId4" display="https://www.indec.gob.ar" xr:uid="{3B42FCC9-8808-4EDE-93A7-F0228BD41018}"/>
+    <hyperlink ref="E25" r:id="rId5" xr:uid="{7362EF37-2A22-4D09-8EC4-151BA22CDD08}"/>
+    <hyperlink ref="E26:E31" r:id="rId6" display="https://www.indec.gob.ar" xr:uid="{181371F1-EAAE-4810-8933-9D89CDD1928B}"/>
+    <hyperlink ref="E32" r:id="rId7" xr:uid="{9297117E-8D72-4F38-9F1C-0AA5B4696F0A}"/>
+    <hyperlink ref="E33:E41" r:id="rId8" display="https://www.indec.gob.ar" xr:uid="{2806D78C-8E30-4025-9799-F7DF1797C643}"/>
+    <hyperlink ref="E42" r:id="rId9" xr:uid="{9F861BF9-FBE3-4D68-BAC0-EAA35FE9FB34}"/>
+    <hyperlink ref="E43:E49" r:id="rId10" display="https://www.indec.gob.ar" xr:uid="{C9E4B419-0DE6-4110-AEFE-A82E1CB79C2F}"/>
+    <hyperlink ref="E50" r:id="rId11" xr:uid="{15FAFF3D-2F48-4076-88AA-BBA4C2B7EC2D}"/>
+    <hyperlink ref="E51:E58" r:id="rId12" display="https://www.indec.gob.ar" xr:uid="{9E9E376A-2A8A-4C3F-B19F-8187BBFF29A6}"/>
+    <hyperlink ref="E59" r:id="rId13" xr:uid="{83A6D2E9-840C-4217-AB1D-DE5830B04CDA}"/>
+    <hyperlink ref="E60:E65" r:id="rId14" display="https://www.indec.gob.ar" xr:uid="{379F007A-C006-46C2-9D3D-C0EC7A5EF762}"/>
+    <hyperlink ref="E66" r:id="rId15" xr:uid="{4F7F4EDC-5326-48FD-A346-11471096DAC6}"/>
+    <hyperlink ref="E67:E72" r:id="rId16" display="https://www.indec.gob.ar" xr:uid="{6B2DAFC2-2A0B-447C-A2C3-C95C48E79112}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/data/excel.xlsx
+++ b/data/excel.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\abiga\Documents\New project\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{22B8FEE6-582F-4717-8221-B66C94B19A99}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F52C09B8-DD61-4D36-AD6F-BED4F7BCABA5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="AZUCAR" sheetId="4" r:id="rId1"/>
@@ -29,7 +29,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1771" uniqueCount="443">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1793" uniqueCount="444">
   <si>
     <t>Bolsa ingenio</t>
   </si>
@@ -1358,6 +1358,9 @@
   </si>
   <si>
     <t>SUSTANCIA</t>
+  </si>
+  <si>
+    <t>TONELADA</t>
   </si>
 </sst>
 </file>
@@ -1466,7 +1469,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="21">
+  <cellXfs count="20">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -1506,10 +1509,9 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Hipervínculo" xfId="1" builtinId="8"/>
@@ -3664,18 +3666,18 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0756568B-799C-4417-9FD5-CA21567FA36E}">
-  <dimension ref="A1:H22"/>
+  <dimension ref="A1:I22"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="10.85546875" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="16.85546875" customWidth="1"/>
     <col min="2" max="2" width="15.42578125" style="1" customWidth="1"/>
-    <col min="3" max="3" width="25.140625" style="1" customWidth="1"/>
-    <col min="4" max="4" width="20.140625" style="1" customWidth="1"/>
-    <col min="5" max="5" width="15.85546875" customWidth="1"/>
-    <col min="6" max="6" width="50.7109375" customWidth="1"/>
+    <col min="3" max="4" width="25.140625" style="1" customWidth="1"/>
+    <col min="5" max="5" width="20.140625" style="1" customWidth="1"/>
+    <col min="6" max="6" width="15.85546875" customWidth="1"/>
+    <col min="7" max="7" width="50.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" ht="18.75" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:9" ht="18.75" x14ac:dyDescent="0.3">
       <c r="A1" s="7" t="s">
         <v>49</v>
       </c>
@@ -3686,16 +3688,19 @@
         <v>51</v>
       </c>
       <c r="D1" s="10" t="s">
+        <v>72</v>
+      </c>
+      <c r="E1" s="10" t="s">
         <v>52</v>
       </c>
-      <c r="E1" s="10" t="s">
+      <c r="F1" s="10" t="s">
         <v>34</v>
       </c>
-      <c r="F1" s="10" t="s">
+      <c r="G1" s="10" t="s">
         <v>13</v>
       </c>
     </row>
-    <row r="2" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A2" s="8" t="s">
         <v>39</v>
       </c>
@@ -3705,17 +3710,20 @@
       <c r="C2" s="4">
         <v>260000</v>
       </c>
-      <c r="D2" s="4">
+      <c r="D2" s="4" t="s">
+        <v>443</v>
+      </c>
+      <c r="E2" s="4">
         <v>251</v>
       </c>
-      <c r="E2" s="8" t="s">
+      <c r="F2" s="8" t="s">
         <v>37</v>
       </c>
-      <c r="F2" s="9" t="s">
+      <c r="G2" s="9" t="s">
         <v>38</v>
       </c>
     </row>
-    <row r="3" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A3" s="8" t="s">
         <v>39</v>
       </c>
@@ -3725,17 +3733,20 @@
       <c r="C3" s="4">
         <v>265000</v>
       </c>
-      <c r="D3" s="4">
+      <c r="D3" s="4" t="s">
+        <v>443</v>
+      </c>
+      <c r="E3" s="4">
         <v>260</v>
       </c>
-      <c r="E3" s="8" t="s">
+      <c r="F3" s="8" t="s">
         <v>37</v>
       </c>
-      <c r="F3" s="9" t="s">
+      <c r="G3" s="9" t="s">
         <v>38</v>
       </c>
     </row>
-    <row r="4" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A4" s="8" t="s">
         <v>39</v>
       </c>
@@ -3745,17 +3756,20 @@
       <c r="C4" s="4">
         <v>270000</v>
       </c>
-      <c r="D4" s="4">
+      <c r="D4" s="4" t="s">
+        <v>443</v>
+      </c>
+      <c r="E4" s="4">
         <v>263.5</v>
       </c>
-      <c r="E4" s="8" t="s">
+      <c r="F4" s="8" t="s">
         <v>37</v>
       </c>
-      <c r="F4" s="9" t="s">
+      <c r="G4" s="9" t="s">
         <v>38</v>
       </c>
     </row>
-    <row r="5" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A5" s="8" t="s">
         <v>39</v>
       </c>
@@ -3765,17 +3779,20 @@
       <c r="C5" s="4">
         <v>250000</v>
       </c>
-      <c r="D5" s="4">
+      <c r="D5" s="4" t="s">
+        <v>443</v>
+      </c>
+      <c r="E5" s="4">
         <v>245</v>
       </c>
-      <c r="E5" s="8" t="s">
+      <c r="F5" s="8" t="s">
         <v>53</v>
       </c>
-      <c r="F5" s="9" t="s">
+      <c r="G5" s="9" t="s">
         <v>45</v>
       </c>
     </row>
-    <row r="6" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A6" s="8" t="s">
         <v>39</v>
       </c>
@@ -3785,17 +3802,20 @@
       <c r="C6" s="4">
         <v>235000</v>
       </c>
-      <c r="D6" s="4">
+      <c r="D6" s="4" t="s">
+        <v>443</v>
+      </c>
+      <c r="E6" s="4">
         <v>230</v>
       </c>
-      <c r="E6" s="8" t="s">
+      <c r="F6" s="8" t="s">
         <v>53</v>
       </c>
-      <c r="F6" s="9" t="s">
+      <c r="G6" s="9" t="s">
         <v>45</v>
       </c>
     </row>
-    <row r="7" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A7" s="8" t="s">
         <v>39</v>
       </c>
@@ -3805,17 +3825,20 @@
       <c r="C7" s="4">
         <v>500000</v>
       </c>
-      <c r="D7" s="4">
+      <c r="D7" s="4" t="s">
+        <v>443</v>
+      </c>
+      <c r="E7" s="4">
         <v>480</v>
       </c>
-      <c r="E7" s="8" t="s">
+      <c r="F7" s="8" t="s">
         <v>53</v>
       </c>
-      <c r="F7" s="9" t="s">
+      <c r="G7" s="9" t="s">
         <v>45</v>
       </c>
     </row>
-    <row r="8" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A8" s="8" t="s">
         <v>35</v>
       </c>
@@ -3825,17 +3848,20 @@
       <c r="C8" s="4">
         <v>465000</v>
       </c>
-      <c r="D8" s="4">
+      <c r="D8" s="4" t="s">
+        <v>443</v>
+      </c>
+      <c r="E8" s="4">
         <v>465</v>
       </c>
-      <c r="E8" s="8" t="s">
+      <c r="F8" s="8" t="s">
         <v>37</v>
       </c>
-      <c r="F8" s="9" t="s">
+      <c r="G8" s="9" t="s">
         <v>38</v>
       </c>
     </row>
-    <row r="9" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A9" s="8" t="s">
         <v>35</v>
       </c>
@@ -3845,17 +3871,20 @@
       <c r="C9" s="4">
         <v>540000</v>
       </c>
-      <c r="D9" s="4">
+      <c r="D9" s="4" t="s">
+        <v>443</v>
+      </c>
+      <c r="E9" s="4">
         <v>534.66</v>
       </c>
-      <c r="E9" s="8" t="s">
+      <c r="F9" s="8" t="s">
         <v>37</v>
       </c>
-      <c r="F9" s="9" t="s">
+      <c r="G9" s="9" t="s">
         <v>38</v>
       </c>
     </row>
-    <row r="10" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A10" s="8" t="s">
         <v>35</v>
       </c>
@@ -3865,17 +3894,20 @@
       <c r="C10" s="4">
         <v>620000</v>
       </c>
-      <c r="D10" s="4">
+      <c r="D10" s="4" t="s">
+        <v>443</v>
+      </c>
+      <c r="E10" s="4">
         <v>620</v>
       </c>
-      <c r="E10" s="8" t="s">
+      <c r="F10" s="8" t="s">
         <v>53</v>
       </c>
-      <c r="F10" s="9" t="s">
+      <c r="G10" s="9" t="s">
         <v>45</v>
       </c>
     </row>
-    <row r="11" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A11" s="8" t="s">
         <v>35</v>
       </c>
@@ -3885,17 +3917,20 @@
       <c r="C11" s="4">
         <v>420000</v>
       </c>
-      <c r="D11" s="4">
+      <c r="D11" s="4" t="s">
+        <v>443</v>
+      </c>
+      <c r="E11" s="4">
         <v>420</v>
       </c>
-      <c r="E11" s="8" t="s">
+      <c r="F11" s="8" t="s">
         <v>53</v>
       </c>
-      <c r="F11" s="9" t="s">
+      <c r="G11" s="9" t="s">
         <v>45</v>
       </c>
     </row>
-    <row r="12" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A12" s="8" t="s">
         <v>35</v>
       </c>
@@ -3905,17 +3940,20 @@
       <c r="C12" s="4">
         <v>980000</v>
       </c>
-      <c r="D12" s="4">
+      <c r="D12" s="4" t="s">
+        <v>443</v>
+      </c>
+      <c r="E12" s="4">
         <v>980</v>
       </c>
-      <c r="E12" s="8" t="s">
+      <c r="F12" s="8" t="s">
         <v>53</v>
       </c>
-      <c r="F12" s="9" t="s">
+      <c r="G12" s="9" t="s">
         <v>45</v>
       </c>
     </row>
-    <row r="13" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A13" s="8" t="s">
         <v>44</v>
       </c>
@@ -3925,17 +3963,20 @@
       <c r="C13" s="4">
         <v>680000</v>
       </c>
-      <c r="D13" s="4">
+      <c r="D13" s="4" t="s">
+        <v>443</v>
+      </c>
+      <c r="E13" s="4">
         <v>680</v>
       </c>
-      <c r="E13" s="8" t="s">
+      <c r="F13" s="8" t="s">
         <v>53</v>
       </c>
-      <c r="F13" s="9" t="s">
+      <c r="G13" s="9" t="s">
         <v>45</v>
       </c>
     </row>
-    <row r="14" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A14" s="8" t="s">
         <v>44</v>
       </c>
@@ -3945,18 +3986,21 @@
       <c r="C14" s="4">
         <v>770000</v>
       </c>
-      <c r="D14" s="4">
+      <c r="D14" s="4" t="s">
+        <v>443</v>
+      </c>
+      <c r="E14" s="4">
         <v>750</v>
       </c>
-      <c r="E14" s="8" t="s">
+      <c r="F14" s="8" t="s">
         <v>53</v>
       </c>
-      <c r="F14" s="9" t="s">
+      <c r="G14" s="9" t="s">
         <v>45</v>
       </c>
-      <c r="H14" s="17"/>
-    </row>
-    <row r="15" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I14" s="19"/>
+    </row>
+    <row r="15" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A15" s="8" t="s">
         <v>44</v>
       </c>
@@ -3966,17 +4010,20 @@
       <c r="C15" s="4">
         <v>920000</v>
       </c>
-      <c r="D15" s="4">
+      <c r="D15" s="4" t="s">
+        <v>443</v>
+      </c>
+      <c r="E15" s="4">
         <v>900</v>
       </c>
-      <c r="E15" s="8" t="s">
+      <c r="F15" s="8" t="s">
         <v>53</v>
       </c>
-      <c r="F15" s="9" t="s">
+      <c r="G15" s="9" t="s">
         <v>45</v>
       </c>
     </row>
-    <row r="16" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A16" s="8" t="s">
         <v>44</v>
       </c>
@@ -3986,17 +4033,20 @@
       <c r="C16" s="4">
         <v>1100000</v>
       </c>
-      <c r="D16" s="4">
+      <c r="D16" s="4" t="s">
+        <v>443</v>
+      </c>
+      <c r="E16" s="4">
         <v>1100</v>
       </c>
-      <c r="E16" s="8" t="s">
+      <c r="F16" s="8" t="s">
         <v>53</v>
       </c>
-      <c r="F16" s="9" t="s">
+      <c r="G16" s="9" t="s">
         <v>45</v>
       </c>
     </row>
-    <row r="17" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A17" s="8" t="s">
         <v>63</v>
       </c>
@@ -4006,17 +4056,20 @@
       <c r="C17" s="4">
         <v>1800000</v>
       </c>
-      <c r="D17" s="4">
+      <c r="D17" s="4" t="s">
+        <v>443</v>
+      </c>
+      <c r="E17" s="4">
         <v>1800</v>
       </c>
-      <c r="E17" s="8" t="s">
+      <c r="F17" s="8" t="s">
         <v>53</v>
       </c>
-      <c r="F17" s="9" t="s">
+      <c r="G17" s="9" t="s">
         <v>45</v>
       </c>
     </row>
-    <row r="18" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A18" s="8" t="s">
         <v>63</v>
       </c>
@@ -4026,17 +4079,20 @@
       <c r="C18" s="4">
         <v>1650000</v>
       </c>
-      <c r="D18" s="4">
+      <c r="D18" s="4" t="s">
+        <v>443</v>
+      </c>
+      <c r="E18" s="4">
         <v>1600</v>
       </c>
-      <c r="E18" s="8" t="s">
+      <c r="F18" s="8" t="s">
         <v>53</v>
       </c>
-      <c r="F18" s="9" t="s">
+      <c r="G18" s="9" t="s">
         <v>45</v>
       </c>
     </row>
-    <row r="19" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A19" s="8" t="s">
         <v>63</v>
       </c>
@@ -4046,17 +4102,20 @@
       <c r="C19" s="4">
         <v>2300000</v>
       </c>
-      <c r="D19" s="4">
+      <c r="D19" s="4" t="s">
+        <v>443</v>
+      </c>
+      <c r="E19" s="4">
         <v>2200</v>
       </c>
-      <c r="E19" s="8" t="s">
+      <c r="F19" s="8" t="s">
         <v>53</v>
       </c>
-      <c r="F19" s="9" t="s">
+      <c r="G19" s="9" t="s">
         <v>45</v>
       </c>
     </row>
-    <row r="20" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A20" s="8" t="s">
         <v>67</v>
       </c>
@@ -4066,17 +4125,20 @@
       <c r="C20" s="4">
         <v>880000</v>
       </c>
-      <c r="D20" s="4">
+      <c r="D20" s="4" t="s">
+        <v>443</v>
+      </c>
+      <c r="E20" s="4">
         <v>850</v>
       </c>
-      <c r="E20" s="8" t="s">
+      <c r="F20" s="8" t="s">
         <v>53</v>
       </c>
-      <c r="F20" s="9" t="s">
+      <c r="G20" s="9" t="s">
         <v>45</v>
       </c>
     </row>
-    <row r="21" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A21" s="8" t="s">
         <v>67</v>
       </c>
@@ -4086,17 +4148,20 @@
       <c r="C21" s="4">
         <v>400000</v>
       </c>
-      <c r="D21" s="4">
+      <c r="D21" s="4" t="s">
+        <v>443</v>
+      </c>
+      <c r="E21" s="4">
         <v>390</v>
       </c>
-      <c r="E21" s="8" t="s">
+      <c r="F21" s="8" t="s">
         <v>53</v>
       </c>
-      <c r="F21" s="9" t="s">
+      <c r="G21" s="9" t="s">
         <v>45</v>
       </c>
     </row>
-    <row r="22" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A22" s="8" t="s">
         <v>35</v>
       </c>
@@ -4106,29 +4171,32 @@
       <c r="C22" s="4">
         <v>6500000</v>
       </c>
-      <c r="D22" s="4">
+      <c r="D22" s="4" t="s">
+        <v>443</v>
+      </c>
+      <c r="E22" s="4">
         <v>6500</v>
       </c>
-      <c r="E22" s="8" t="s">
+      <c r="F22" s="8" t="s">
         <v>53</v>
       </c>
-      <c r="F22" s="16" t="s">
+      <c r="G22" s="16" t="s">
         <v>45</v>
       </c>
     </row>
   </sheetData>
   <hyperlinks>
-    <hyperlink ref="F2" r:id="rId1" xr:uid="{2153F076-65FB-49BD-8315-B1AA22D485AF}"/>
-    <hyperlink ref="F3:F4" r:id="rId2" display="https://www.bcr.com.ar/es/mercados/mercado-de-granos" xr:uid="{5BA120F2-97AF-428E-B044-B48F27371B76}"/>
-    <hyperlink ref="F5" r:id="rId3" xr:uid="{A87F1914-9789-4410-B6A6-1C41B4B1998C}"/>
-    <hyperlink ref="F6" r:id="rId4" xr:uid="{FCFF2620-3142-4A39-BD65-33C2CD4DBCF2}"/>
-    <hyperlink ref="F7" r:id="rId5" xr:uid="{FEC39A7A-0967-4793-B9F6-67C43077C2FA}"/>
-    <hyperlink ref="F8" r:id="rId6" xr:uid="{8F1A3BFD-2DB5-4AA2-A136-2F4E6822A7DE}"/>
-    <hyperlink ref="F9" r:id="rId7" xr:uid="{C66C55DD-844A-43D2-8924-D84507B3EB22}"/>
-    <hyperlink ref="F10" r:id="rId8" xr:uid="{5A0D2826-6BD4-495E-8193-A0BDD2A7B4B5}"/>
-    <hyperlink ref="F11:F21" r:id="rId9" display="https://www.magyp.gob.ar" xr:uid="{53FAAE7D-1E0C-4C14-9351-1261159A1DC2}"/>
-    <hyperlink ref="F12" r:id="rId10" xr:uid="{91A690C0-1C99-493B-8A96-9A7B684D5451}"/>
-    <hyperlink ref="F22" r:id="rId11" xr:uid="{67B1D3AB-64F6-4733-9A48-5F1D9844E807}"/>
+    <hyperlink ref="G2" r:id="rId1" xr:uid="{2153F076-65FB-49BD-8315-B1AA22D485AF}"/>
+    <hyperlink ref="G3:G4" r:id="rId2" display="https://www.bcr.com.ar/es/mercados/mercado-de-granos" xr:uid="{5BA120F2-97AF-428E-B044-B48F27371B76}"/>
+    <hyperlink ref="G5" r:id="rId3" xr:uid="{A87F1914-9789-4410-B6A6-1C41B4B1998C}"/>
+    <hyperlink ref="G6" r:id="rId4" xr:uid="{FCFF2620-3142-4A39-BD65-33C2CD4DBCF2}"/>
+    <hyperlink ref="G7" r:id="rId5" xr:uid="{FEC39A7A-0967-4793-B9F6-67C43077C2FA}"/>
+    <hyperlink ref="G8" r:id="rId6" xr:uid="{8F1A3BFD-2DB5-4AA2-A136-2F4E6822A7DE}"/>
+    <hyperlink ref="G9" r:id="rId7" xr:uid="{C66C55DD-844A-43D2-8924-D84507B3EB22}"/>
+    <hyperlink ref="G10" r:id="rId8" xr:uid="{5A0D2826-6BD4-495E-8193-A0BDD2A7B4B5}"/>
+    <hyperlink ref="G11:G21" r:id="rId9" display="https://www.magyp.gob.ar" xr:uid="{53FAAE7D-1E0C-4C14-9351-1261159A1DC2}"/>
+    <hyperlink ref="G12" r:id="rId10" xr:uid="{91A690C0-1C99-493B-8A96-9A7B684D5451}"/>
+    <hyperlink ref="G22" r:id="rId11" xr:uid="{67B1D3AB-64F6-4733-9A48-5F1D9844E807}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -4136,7 +4204,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{15575E2F-B7E9-4EB5-A791-7D7E5CF1065C}">
-  <dimension ref="A1:E6"/>
+  <dimension ref="A1:E3"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="17.7109375" customWidth="1"/>
@@ -4162,7 +4230,7 @@
       </c>
     </row>
     <row r="2" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A2" s="18" t="s">
+      <c r="A2" s="17" t="s">
         <v>438</v>
       </c>
       <c r="B2" t="s">
@@ -4188,9 +4256,6 @@
       <c r="D3">
         <v>14000</v>
       </c>
-    </row>
-    <row r="6" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="B6" s="19"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -6360,7 +6425,7 @@
       </c>
     </row>
     <row r="73" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A73" s="20" t="s">
+      <c r="A73" s="18" t="s">
         <v>441</v>
       </c>
       <c r="B73" s="8" t="s">

--- a/data/excel.xlsx
+++ b/data/excel.xlsx
@@ -8,14 +8,14 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\abiga\Documents\New project\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F52C09B8-DD61-4D36-AD6F-BED4F7BCABA5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EC416467-F4A7-49DB-A361-5C7340EE212F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" firstSheet="1" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="AZUCAR" sheetId="4" r:id="rId1"/>
     <sheet name="GRANOS" sheetId="6" r:id="rId2"/>
-    <sheet name="Hoja2" sheetId="14" r:id="rId3"/>
+    <sheet name="22415" sheetId="14" r:id="rId3"/>
     <sheet name="PLASTICOS" sheetId="9" r:id="rId4"/>
     <sheet name="MADERA" sheetId="10" r:id="rId5"/>
     <sheet name="MATERIALES DE CONSTRUCCION" sheetId="7" r:id="rId6"/>
@@ -29,7 +29,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1793" uniqueCount="444">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1798" uniqueCount="448">
   <si>
     <t>Bolsa ingenio</t>
   </si>
@@ -1342,12 +1342,6 @@
     <t>CLORHIDRATO DE COCAINA</t>
   </si>
   <si>
-    <t>estupefaciente</t>
-  </si>
-  <si>
-    <t>planta </t>
-  </si>
-  <si>
     <t>https://informatesalta.com.ar/sociedad/la-hoja-de-coca-subio-un-30--y-se-consigue-el-kilo-de-la-hojeada-hasta--45-000_a6a15916a03d1047930dc412f</t>
   </si>
   <si>
@@ -1360,7 +1354,25 @@
     <t>SUSTANCIA</t>
   </si>
   <si>
-    <t>TONELADA</t>
+    <t>KILOGRAMO</t>
+  </si>
+  <si>
+    <t>DROGA</t>
+  </si>
+  <si>
+    <t xml:space="preserve">UNIDAD </t>
+  </si>
+  <si>
+    <t xml:space="preserve">NEUMATICOS </t>
+  </si>
+  <si>
+    <t>CUBIERTAS| AUTO</t>
+  </si>
+  <si>
+    <t>CUBIERTAS| MOTO</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CUBIERTAS| CAMIÓN </t>
   </si>
 </sst>
 </file>
@@ -1511,7 +1523,9 @@
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Hipervínculo" xfId="1" builtinId="8"/>
@@ -3666,7 +3680,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0756568B-799C-4417-9FD5-CA21567FA36E}">
-  <dimension ref="A1:I22"/>
+  <dimension ref="A1:G25"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="10.85546875" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="16.85546875" customWidth="1"/>
@@ -3677,7 +3691,7 @@
     <col min="7" max="7" width="50.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:9" ht="18.75" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:7" ht="18.75" x14ac:dyDescent="0.3">
       <c r="A1" s="7" t="s">
         <v>49</v>
       </c>
@@ -3700,7 +3714,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="2" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A2" s="8" t="s">
         <v>39</v>
       </c>
@@ -3708,10 +3722,10 @@
         <v>40</v>
       </c>
       <c r="C2" s="4">
-        <v>260000</v>
+        <v>260</v>
       </c>
       <c r="D2" s="4" t="s">
-        <v>443</v>
+        <v>441</v>
       </c>
       <c r="E2" s="4">
         <v>251</v>
@@ -3723,7 +3737,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="3" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A3" s="8" t="s">
         <v>39</v>
       </c>
@@ -3731,10 +3745,10 @@
         <v>41</v>
       </c>
       <c r="C3" s="4">
-        <v>265000</v>
+        <v>265</v>
       </c>
       <c r="D3" s="4" t="s">
-        <v>443</v>
+        <v>441</v>
       </c>
       <c r="E3" s="4">
         <v>260</v>
@@ -3746,7 +3760,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="4" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A4" s="8" t="s">
         <v>39</v>
       </c>
@@ -3754,10 +3768,10 @@
         <v>42</v>
       </c>
       <c r="C4" s="4">
-        <v>270000</v>
+        <v>270</v>
       </c>
       <c r="D4" s="4" t="s">
-        <v>443</v>
+        <v>441</v>
       </c>
       <c r="E4" s="4">
         <v>263.5</v>
@@ -3769,7 +3783,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="5" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A5" s="8" t="s">
         <v>39</v>
       </c>
@@ -3777,10 +3791,10 @@
         <v>46</v>
       </c>
       <c r="C5" s="4">
-        <v>250000</v>
+        <v>250</v>
       </c>
       <c r="D5" s="4" t="s">
-        <v>443</v>
+        <v>441</v>
       </c>
       <c r="E5" s="4">
         <v>245</v>
@@ -3792,7 +3806,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="6" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A6" s="8" t="s">
         <v>39</v>
       </c>
@@ -3800,10 +3814,10 @@
         <v>54</v>
       </c>
       <c r="C6" s="4">
-        <v>235000</v>
+        <v>235</v>
       </c>
       <c r="D6" s="4" t="s">
-        <v>443</v>
+        <v>441</v>
       </c>
       <c r="E6" s="4">
         <v>230</v>
@@ -3815,7 +3829,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="7" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A7" s="8" t="s">
         <v>39</v>
       </c>
@@ -3823,10 +3837,10 @@
         <v>55</v>
       </c>
       <c r="C7" s="4">
-        <v>500000</v>
+        <v>500</v>
       </c>
       <c r="D7" s="4" t="s">
-        <v>443</v>
+        <v>441</v>
       </c>
       <c r="E7" s="4">
         <v>480</v>
@@ -3838,7 +3852,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="8" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A8" s="8" t="s">
         <v>35</v>
       </c>
@@ -3846,10 +3860,10 @@
         <v>36</v>
       </c>
       <c r="C8" s="4">
-        <v>465000</v>
+        <v>465</v>
       </c>
       <c r="D8" s="4" t="s">
-        <v>443</v>
+        <v>441</v>
       </c>
       <c r="E8" s="4">
         <v>465</v>
@@ -3861,7 +3875,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="9" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A9" s="8" t="s">
         <v>35</v>
       </c>
@@ -3869,10 +3883,10 @@
         <v>43</v>
       </c>
       <c r="C9" s="4">
-        <v>540000</v>
+        <v>540</v>
       </c>
       <c r="D9" s="4" t="s">
-        <v>443</v>
+        <v>441</v>
       </c>
       <c r="E9" s="4">
         <v>534.66</v>
@@ -3884,7 +3898,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="10" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A10" s="8" t="s">
         <v>35</v>
       </c>
@@ -3892,10 +3906,10 @@
         <v>56</v>
       </c>
       <c r="C10" s="4">
-        <v>620000</v>
+        <v>620</v>
       </c>
       <c r="D10" s="4" t="s">
-        <v>443</v>
+        <v>441</v>
       </c>
       <c r="E10" s="4">
         <v>620</v>
@@ -3907,7 +3921,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="11" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A11" s="8" t="s">
         <v>35</v>
       </c>
@@ -3915,10 +3929,10 @@
         <v>57</v>
       </c>
       <c r="C11" s="4">
-        <v>420000</v>
+        <v>420</v>
       </c>
       <c r="D11" s="4" t="s">
-        <v>443</v>
+        <v>441</v>
       </c>
       <c r="E11" s="4">
         <v>420</v>
@@ -3930,7 +3944,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="12" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A12" s="8" t="s">
         <v>35</v>
       </c>
@@ -3938,10 +3952,10 @@
         <v>58</v>
       </c>
       <c r="C12" s="4">
-        <v>980000</v>
+        <v>980</v>
       </c>
       <c r="D12" s="4" t="s">
-        <v>443</v>
+        <v>441</v>
       </c>
       <c r="E12" s="4">
         <v>980</v>
@@ -3953,7 +3967,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="13" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A13" s="8" t="s">
         <v>44</v>
       </c>
@@ -3961,10 +3975,10 @@
         <v>59</v>
       </c>
       <c r="C13" s="4">
-        <v>680000</v>
+        <v>680</v>
       </c>
       <c r="D13" s="4" t="s">
-        <v>443</v>
+        <v>441</v>
       </c>
       <c r="E13" s="4">
         <v>680</v>
@@ -3976,7 +3990,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="14" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A14" s="8" t="s">
         <v>44</v>
       </c>
@@ -3984,10 +3998,10 @@
         <v>60</v>
       </c>
       <c r="C14" s="4">
-        <v>770000</v>
+        <v>770</v>
       </c>
       <c r="D14" s="4" t="s">
-        <v>443</v>
+        <v>441</v>
       </c>
       <c r="E14" s="4">
         <v>750</v>
@@ -3998,9 +4012,8 @@
       <c r="G14" s="9" t="s">
         <v>45</v>
       </c>
-      <c r="I14" s="19"/>
-    </row>
-    <row r="15" spans="1:9" x14ac:dyDescent="0.25">
+    </row>
+    <row r="15" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A15" s="8" t="s">
         <v>44</v>
       </c>
@@ -4008,10 +4021,10 @@
         <v>61</v>
       </c>
       <c r="C15" s="4">
-        <v>920000</v>
+        <v>920</v>
       </c>
       <c r="D15" s="4" t="s">
-        <v>443</v>
+        <v>441</v>
       </c>
       <c r="E15" s="4">
         <v>900</v>
@@ -4023,7 +4036,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="16" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A16" s="8" t="s">
         <v>44</v>
       </c>
@@ -4031,10 +4044,10 @@
         <v>62</v>
       </c>
       <c r="C16" s="4">
-        <v>1100000</v>
+        <v>1100</v>
       </c>
       <c r="D16" s="4" t="s">
-        <v>443</v>
+        <v>441</v>
       </c>
       <c r="E16" s="4">
         <v>1100</v>
@@ -4054,10 +4067,10 @@
         <v>64</v>
       </c>
       <c r="C17" s="4">
-        <v>1800000</v>
+        <v>1800</v>
       </c>
       <c r="D17" s="4" t="s">
-        <v>443</v>
+        <v>441</v>
       </c>
       <c r="E17" s="4">
         <v>1800</v>
@@ -4077,10 +4090,10 @@
         <v>65</v>
       </c>
       <c r="C18" s="4">
-        <v>1650000</v>
+        <v>1650</v>
       </c>
       <c r="D18" s="4" t="s">
-        <v>443</v>
+        <v>441</v>
       </c>
       <c r="E18" s="4">
         <v>1600</v>
@@ -4100,10 +4113,10 @@
         <v>66</v>
       </c>
       <c r="C19" s="4">
-        <v>2300000</v>
+        <v>2300</v>
       </c>
       <c r="D19" s="4" t="s">
-        <v>443</v>
+        <v>441</v>
       </c>
       <c r="E19" s="4">
         <v>2200</v>
@@ -4123,10 +4136,10 @@
         <v>68</v>
       </c>
       <c r="C20" s="4">
-        <v>880000</v>
+        <v>880</v>
       </c>
       <c r="D20" s="4" t="s">
-        <v>443</v>
+        <v>441</v>
       </c>
       <c r="E20" s="4">
         <v>850</v>
@@ -4146,10 +4159,10 @@
         <v>69</v>
       </c>
       <c r="C21" s="4">
-        <v>400000</v>
+        <v>400</v>
       </c>
       <c r="D21" s="4" t="s">
-        <v>443</v>
+        <v>441</v>
       </c>
       <c r="E21" s="4">
         <v>390</v>
@@ -4169,10 +4182,10 @@
         <v>431</v>
       </c>
       <c r="C22" s="4">
-        <v>6500000</v>
+        <v>6500</v>
       </c>
       <c r="D22" s="4" t="s">
-        <v>443</v>
+        <v>441</v>
       </c>
       <c r="E22" s="4">
         <v>6500</v>
@@ -4183,6 +4196,18 @@
       <c r="G22" s="16" t="s">
         <v>45</v>
       </c>
+    </row>
+    <row r="23" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="C23" s="19"/>
+      <c r="D23" s="19"/>
+    </row>
+    <row r="24" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="C24" s="19"/>
+      <c r="D24" s="19"/>
+    </row>
+    <row r="25" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="C25" s="19"/>
+      <c r="D25" s="19"/>
     </row>
   </sheetData>
   <hyperlinks>
@@ -4204,11 +4229,13 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{15575E2F-B7E9-4EB5-A791-7D7E5CF1065C}">
-  <dimension ref="A1:E3"/>
+  <dimension ref="A1:E6"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="17.7109375" customWidth="1"/>
     <col min="2" max="2" width="32.7109375" customWidth="1"/>
+    <col min="3" max="3" width="30.28515625" customWidth="1"/>
+    <col min="4" max="4" width="40.28515625" customWidth="1"/>
     <col min="5" max="5" width="23.7109375" customWidth="1"/>
   </cols>
   <sheetData>
@@ -4220,7 +4247,7 @@
         <v>50</v>
       </c>
       <c r="C1" s="10" t="s">
-        <v>51</v>
+        <v>72</v>
       </c>
       <c r="D1" s="10" t="s">
         <v>52</v>
@@ -4231,7 +4258,7 @@
     </row>
     <row r="2" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A2" s="17" t="s">
-        <v>438</v>
+        <v>439</v>
       </c>
       <c r="B2" t="s">
         <v>433</v>
@@ -4245,7 +4272,7 @@
     </row>
     <row r="3" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>437</v>
+        <v>442</v>
       </c>
       <c r="B3" t="s">
         <v>436</v>
@@ -4255,6 +4282,48 @@
       </c>
       <c r="D3">
         <v>14000</v>
+      </c>
+    </row>
+    <row r="4" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A4" t="s">
+        <v>444</v>
+      </c>
+      <c r="B4" t="s">
+        <v>445</v>
+      </c>
+      <c r="C4" t="s">
+        <v>443</v>
+      </c>
+      <c r="D4">
+        <v>110000</v>
+      </c>
+    </row>
+    <row r="5" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A5" t="s">
+        <v>444</v>
+      </c>
+      <c r="B5" t="s">
+        <v>446</v>
+      </c>
+      <c r="C5" t="s">
+        <v>443</v>
+      </c>
+      <c r="D5">
+        <v>75000</v>
+      </c>
+    </row>
+    <row r="6" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A6" t="s">
+        <v>444</v>
+      </c>
+      <c r="B6" t="s">
+        <v>447</v>
+      </c>
+      <c r="C6" t="s">
+        <v>443</v>
+      </c>
+      <c r="D6">
+        <v>400000</v>
       </c>
     </row>
   </sheetData>
@@ -6426,7 +6495,7 @@
     </row>
     <row r="73" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A73" s="18" t="s">
-        <v>441</v>
+        <v>439</v>
       </c>
       <c r="B73" s="8" t="s">
         <v>433</v>
@@ -6438,12 +6507,12 @@
         <v>40000</v>
       </c>
       <c r="E73" s="8" t="s">
-        <v>439</v>
+        <v>437</v>
       </c>
     </row>
     <row r="74" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A74" s="8" t="s">
-        <v>442</v>
+        <v>440</v>
       </c>
       <c r="B74" s="8" t="s">
         <v>436</v>
@@ -6455,7 +6524,7 @@
         <v>14000</v>
       </c>
       <c r="E74" t="s">
-        <v>440</v>
+        <v>438</v>
       </c>
     </row>
   </sheetData>
@@ -9622,7 +9691,7 @@
 
 <file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{748F122F-7CC3-499F-98B9-01D3B28FD4BC}">
-  <dimension ref="A1:E3"/>
+  <dimension ref="A1:E1"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="21.5703125" customWidth="1"/>
@@ -9649,28 +9718,6 @@
         <v>333</v>
       </c>
     </row>
-    <row r="2" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="B2" t="s">
-        <v>433</v>
-      </c>
-      <c r="C2" t="s">
-        <v>434</v>
-      </c>
-      <c r="D2">
-        <v>40000</v>
-      </c>
-    </row>
-    <row r="3" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="B3" t="s">
-        <v>436</v>
-      </c>
-      <c r="C3" t="s">
-        <v>435</v>
-      </c>
-      <c r="D3">
-        <v>14000</v>
-      </c>
-    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
